--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123818966</v>
+        <v>123819157</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>78431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572304</v>
+        <v>572446</v>
       </c>
       <c r="R2" t="n">
-        <v>6462690</v>
+        <v>6462925</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123818331</v>
+        <v>123818639</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>78431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572576</v>
+        <v>572466</v>
       </c>
       <c r="R3" t="n">
-        <v>6462698</v>
+        <v>6462822</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123818454</v>
+        <v>123819031</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>5492</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +899,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572542</v>
+        <v>572284</v>
       </c>
       <c r="R4" t="n">
-        <v>6462761</v>
+        <v>6462713</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123818360</v>
+        <v>123818819</v>
       </c>
       <c r="B5" t="n">
-        <v>79399</v>
+        <v>5479</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,30 +1007,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572567</v>
+        <v>572399</v>
       </c>
       <c r="R5" t="n">
-        <v>6462723</v>
+        <v>6462693</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819130</v>
+        <v>123818446</v>
       </c>
       <c r="B6" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,30 +1115,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572378</v>
+        <v>572535</v>
       </c>
       <c r="R6" t="n">
-        <v>6462897</v>
+        <v>6462771</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819098</v>
+        <v>123818960</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,26 +1226,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572307</v>
+        <v>572326</v>
       </c>
       <c r="R7" t="n">
-        <v>6462856</v>
+        <v>6462705</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,13 +1300,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123818873</v>
+        <v>123818415</v>
       </c>
       <c r="B8" t="n">
-        <v>90967</v>
+        <v>95173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,26 +1345,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572422</v>
+        <v>572570</v>
       </c>
       <c r="R8" t="n">
-        <v>6462709</v>
+        <v>6462742</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818763</v>
+        <v>123819081</v>
       </c>
       <c r="B9" t="n">
-        <v>90981</v>
+        <v>5479</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,30 +1448,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1110</v>
+        <v>101920</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572392</v>
+        <v>572275</v>
       </c>
       <c r="R9" t="n">
-        <v>6462722</v>
+        <v>6462841</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818590</v>
+        <v>123819088</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>78431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572563</v>
+        <v>572276</v>
       </c>
       <c r="R10" t="n">
-        <v>6462748</v>
+        <v>6462860</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123818826</v>
+        <v>123819082</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>78431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1666,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572399</v>
+        <v>572275</v>
       </c>
       <c r="R11" t="n">
-        <v>6462693</v>
+        <v>6462841</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1737,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818381</v>
+        <v>123819167</v>
       </c>
       <c r="B12" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572568</v>
+        <v>572447</v>
       </c>
       <c r="R12" t="n">
-        <v>6462684</v>
+        <v>6462925</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123818843</v>
+        <v>123819032</v>
       </c>
       <c r="B13" t="n">
-        <v>78426</v>
+        <v>79404</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572420</v>
+        <v>572284</v>
       </c>
       <c r="R13" t="n">
-        <v>6462720</v>
+        <v>6462713</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123819073</v>
+        <v>123819096</v>
       </c>
       <c r="B14" t="n">
-        <v>78426</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572257</v>
+        <v>572307</v>
       </c>
       <c r="R14" t="n">
-        <v>6462806</v>
+        <v>6462856</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123819177</v>
+        <v>123818763</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>90986</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,25 +2086,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572456</v>
+        <v>572392</v>
       </c>
       <c r="R15" t="n">
-        <v>6462900</v>
+        <v>6462722</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2161,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818916</v>
+        <v>123819172</v>
       </c>
       <c r="B16" t="n">
-        <v>79399</v>
+        <v>90986</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,25 +2192,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572384</v>
+        <v>572456</v>
       </c>
       <c r="R16" t="n">
-        <v>6462675</v>
+        <v>6462900</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2267,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123818438</v>
+        <v>123818454</v>
       </c>
       <c r="B17" t="n">
-        <v>90981</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,30 +2298,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2310,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572538</v>
+        <v>572542</v>
       </c>
       <c r="R17" t="n">
-        <v>6462741</v>
+        <v>6462761</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123818415</v>
+        <v>123818742</v>
       </c>
       <c r="B18" t="n">
-        <v>95167</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2405,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572570</v>
+        <v>572433</v>
       </c>
       <c r="R18" t="n">
-        <v>6462742</v>
+        <v>6462777</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2480,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123818643</v>
+        <v>123819162</v>
       </c>
       <c r="B19" t="n">
-        <v>91003</v>
+        <v>78431</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572466</v>
+        <v>572447</v>
       </c>
       <c r="R19" t="n">
-        <v>6462822</v>
+        <v>6462925</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2586,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819072</v>
+        <v>123818331</v>
       </c>
       <c r="B20" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572298</v>
+        <v>572576</v>
       </c>
       <c r="R20" t="n">
-        <v>6462796</v>
+        <v>6462698</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2692,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819167</v>
+        <v>123818938</v>
       </c>
       <c r="B21" t="n">
-        <v>91003</v>
+        <v>74817</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,25 +2724,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572447</v>
+        <v>572347</v>
       </c>
       <c r="R21" t="n">
-        <v>6462925</v>
+        <v>6462723</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818753</v>
+        <v>123818643</v>
       </c>
       <c r="B22" t="n">
-        <v>78426</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,21 +2834,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2841,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572414</v>
+        <v>572466</v>
       </c>
       <c r="R22" t="n">
-        <v>6462768</v>
+        <v>6462822</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2904,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819032</v>
+        <v>123819084</v>
       </c>
       <c r="B23" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572284</v>
+        <v>572275</v>
       </c>
       <c r="R23" t="n">
-        <v>6462713</v>
+        <v>6462841</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3010,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819173</v>
+        <v>123818426</v>
       </c>
       <c r="B24" t="n">
-        <v>92299</v>
+        <v>92269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3022,25 +3042,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3053,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572456</v>
+        <v>572545</v>
       </c>
       <c r="R24" t="n">
-        <v>6462900</v>
+        <v>6462716</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3116,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819096</v>
+        <v>123819036</v>
       </c>
       <c r="B25" t="n">
-        <v>91003</v>
+        <v>79404</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572307</v>
+        <v>572299</v>
       </c>
       <c r="R25" t="n">
-        <v>6462856</v>
+        <v>6462763</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3222,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123818936</v>
+        <v>123818837</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,31 +3254,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3266,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572347</v>
+        <v>572414</v>
       </c>
       <c r="R26" t="n">
-        <v>6462723</v>
+        <v>6462716</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3329,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819084</v>
+        <v>123818843</v>
       </c>
       <c r="B27" t="n">
-        <v>79399</v>
+        <v>78431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3345,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572275</v>
+        <v>572420</v>
       </c>
       <c r="R27" t="n">
-        <v>6462841</v>
+        <v>6462720</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3435,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818742</v>
+        <v>123818916</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,31 +3466,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3479,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572433</v>
+        <v>572384</v>
       </c>
       <c r="R28" t="n">
-        <v>6462777</v>
+        <v>6462675</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3542,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818345</v>
+        <v>123818852</v>
       </c>
       <c r="B29" t="n">
-        <v>95167</v>
+        <v>79404</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,31 +3572,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3586,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572575</v>
+        <v>572410</v>
       </c>
       <c r="R29" t="n">
-        <v>6462706</v>
+        <v>6462725</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819176</v>
+        <v>123819035</v>
       </c>
       <c r="B30" t="n">
-        <v>91003</v>
+        <v>90988</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3692,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572456</v>
+        <v>572299</v>
       </c>
       <c r="R30" t="n">
-        <v>6462900</v>
+        <v>6462763</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3755,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818411</v>
+        <v>123818753</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>78431</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,31 +3784,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3799,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572570</v>
+        <v>572414</v>
       </c>
       <c r="R31" t="n">
-        <v>6462742</v>
+        <v>6462768</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3862,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819074</v>
+        <v>123818411</v>
       </c>
       <c r="B32" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3874,30 +3890,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3905,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572257</v>
+        <v>572570</v>
       </c>
       <c r="R32" t="n">
-        <v>6462806</v>
+        <v>6462742</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3968,10 +3985,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819025</v>
+        <v>123819158</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3980,31 +3997,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4012,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572337</v>
+        <v>572446</v>
       </c>
       <c r="R33" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4075,10 +4091,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819082</v>
+        <v>123819177</v>
       </c>
       <c r="B34" t="n">
-        <v>78426</v>
+        <v>79404</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4091,21 +4107,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4118,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572275</v>
+        <v>572456</v>
       </c>
       <c r="R34" t="n">
-        <v>6462841</v>
+        <v>6462900</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4181,10 +4197,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819031</v>
+        <v>123819098</v>
       </c>
       <c r="B35" t="n">
-        <v>5490</v>
+        <v>79404</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,28 +4213,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4226,10 +4240,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572284</v>
+        <v>572307</v>
       </c>
       <c r="R35" t="n">
-        <v>6462713</v>
+        <v>6462856</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4289,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123819036</v>
+        <v>123818871</v>
       </c>
       <c r="B36" t="n">
-        <v>79399</v>
+        <v>5492</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,26 +4319,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4332,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572299</v>
+        <v>572422</v>
       </c>
       <c r="R36" t="n">
-        <v>6462763</v>
+        <v>6462709</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4395,10 +4411,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123818629</v>
+        <v>123818345</v>
       </c>
       <c r="B37" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4439,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572515</v>
+        <v>572575</v>
       </c>
       <c r="R37" t="n">
-        <v>6462760</v>
+        <v>6462706</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4502,10 +4518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819081</v>
+        <v>123818388</v>
       </c>
       <c r="B38" t="n">
-        <v>5477</v>
+        <v>79404</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4514,32 +4530,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4547,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572275</v>
+        <v>572560</v>
       </c>
       <c r="R38" t="n">
-        <v>6462841</v>
+        <v>6462694</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4610,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123818938</v>
+        <v>123819173</v>
       </c>
       <c r="B39" t="n">
-        <v>74814</v>
+        <v>92304</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4622,25 +4636,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4653,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572347</v>
+        <v>572456</v>
       </c>
       <c r="R39" t="n">
-        <v>6462723</v>
+        <v>6462900</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4719,7 +4733,7 @@
         <v>123819077</v>
       </c>
       <c r="B40" t="n">
-        <v>78426</v>
+        <v>78431</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4822,10 +4836,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818871</v>
+        <v>123819179</v>
       </c>
       <c r="B41" t="n">
-        <v>5490</v>
+        <v>78431</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4838,28 +4852,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4867,10 +4879,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572422</v>
+        <v>572456</v>
       </c>
       <c r="R41" t="n">
-        <v>6462709</v>
+        <v>6462900</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4930,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819157</v>
+        <v>123818360</v>
       </c>
       <c r="B42" t="n">
-        <v>78426</v>
+        <v>79404</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4946,21 +4958,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4973,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572446</v>
+        <v>572567</v>
       </c>
       <c r="R42" t="n">
-        <v>6462925</v>
+        <v>6462723</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5036,10 +5048,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819162</v>
+        <v>123819072</v>
       </c>
       <c r="B43" t="n">
-        <v>78426</v>
+        <v>79404</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5052,21 +5064,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572447</v>
+        <v>572298</v>
       </c>
       <c r="R43" t="n">
-        <v>6462925</v>
+        <v>6462796</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5142,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123819034</v>
+        <v>123818966</v>
       </c>
       <c r="B44" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5154,30 +5166,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5185,10 +5198,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572277</v>
+        <v>572304</v>
       </c>
       <c r="R44" t="n">
-        <v>6462750</v>
+        <v>6462690</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5248,10 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818446</v>
+        <v>123818542</v>
       </c>
       <c r="B45" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,31 +5273,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5292,10 +5309,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572535</v>
+        <v>572542</v>
       </c>
       <c r="R45" t="n">
-        <v>6462771</v>
+        <v>6462761</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5336,7 +5353,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5355,10 +5371,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819179</v>
+        <v>123819121</v>
       </c>
       <c r="B46" t="n">
-        <v>78426</v>
+        <v>56700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5367,30 +5383,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5398,10 +5427,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572456</v>
+        <v>572362</v>
       </c>
       <c r="R46" t="n">
-        <v>6462900</v>
+        <v>6462874</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5436,13 +5465,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5461,10 +5494,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123818388</v>
+        <v>123818381</v>
       </c>
       <c r="B47" t="n">
-        <v>79399</v>
+        <v>91008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5477,21 +5510,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5504,10 +5537,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572560</v>
+        <v>572568</v>
       </c>
       <c r="R47" t="n">
-        <v>6462694</v>
+        <v>6462684</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5567,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818426</v>
+        <v>123818438</v>
       </c>
       <c r="B48" t="n">
-        <v>92264</v>
+        <v>90986</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5579,25 +5612,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>1110</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5610,10 +5643,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572545</v>
+        <v>572538</v>
       </c>
       <c r="R48" t="n">
-        <v>6462716</v>
+        <v>6462741</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5673,10 +5706,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818639</v>
+        <v>123818936</v>
       </c>
       <c r="B49" t="n">
-        <v>78426</v>
+        <v>98502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5685,30 +5718,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5716,10 +5750,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572466</v>
+        <v>572347</v>
       </c>
       <c r="R49" t="n">
-        <v>6462822</v>
+        <v>6462723</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5779,10 +5813,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818682</v>
+        <v>123819089</v>
       </c>
       <c r="B50" t="n">
-        <v>57503</v>
+        <v>79404</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5795,43 +5829,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5839,10 +5856,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572441</v>
+        <v>572276</v>
       </c>
       <c r="R50" t="n">
-        <v>6462802</v>
+        <v>6462860</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5877,17 +5894,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5906,10 +5919,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818852</v>
+        <v>123819025</v>
       </c>
       <c r="B51" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5918,30 +5931,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5949,10 +5963,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572410</v>
+        <v>572337</v>
       </c>
       <c r="R51" t="n">
-        <v>6462725</v>
+        <v>6462716</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6012,10 +6026,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123819088</v>
+        <v>123818646</v>
       </c>
       <c r="B52" t="n">
-        <v>78426</v>
+        <v>79404</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6028,21 +6042,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6055,10 +6069,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572276</v>
+        <v>572466</v>
       </c>
       <c r="R52" t="n">
-        <v>6462860</v>
+        <v>6462822</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6118,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123819124</v>
+        <v>123819074</v>
       </c>
       <c r="B53" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6161,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572362</v>
+        <v>572257</v>
       </c>
       <c r="R53" t="n">
-        <v>6462874</v>
+        <v>6462806</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6224,10 +6238,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818757</v>
+        <v>123819176</v>
       </c>
       <c r="B54" t="n">
-        <v>79399</v>
+        <v>91008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6240,21 +6254,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6267,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572407</v>
+        <v>572456</v>
       </c>
       <c r="R54" t="n">
-        <v>6462746</v>
+        <v>6462900</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6330,10 +6344,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123818542</v>
+        <v>123818826</v>
       </c>
       <c r="B55" t="n">
-        <v>57503</v>
+        <v>79404</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6346,31 +6360,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6378,10 +6387,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572542</v>
+        <v>572399</v>
       </c>
       <c r="R55" t="n">
-        <v>6462761</v>
+        <v>6462693</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6422,6 +6431,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6440,10 +6450,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818960</v>
+        <v>123818757</v>
       </c>
       <c r="B56" t="n">
-        <v>57640</v>
+        <v>79404</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,35 +6466,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6492,10 +6493,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572326</v>
+        <v>572407</v>
       </c>
       <c r="R56" t="n">
-        <v>6462705</v>
+        <v>6462746</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6530,17 +6531,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6559,10 +6556,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818837</v>
+        <v>123819169</v>
       </c>
       <c r="B57" t="n">
-        <v>91003</v>
+        <v>79404</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6575,21 +6572,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6602,10 +6599,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572414</v>
+        <v>572447</v>
       </c>
       <c r="R57" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6665,10 +6662,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818819</v>
+        <v>123819124</v>
       </c>
       <c r="B58" t="n">
-        <v>5477</v>
+        <v>79404</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6677,32 +6674,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6710,10 +6705,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572399</v>
+        <v>572362</v>
       </c>
       <c r="R58" t="n">
-        <v>6462693</v>
+        <v>6462874</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6773,10 +6768,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819172</v>
+        <v>123818590</v>
       </c>
       <c r="B59" t="n">
-        <v>90981</v>
+        <v>79404</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6785,25 +6780,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6816,10 +6811,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572456</v>
+        <v>572563</v>
       </c>
       <c r="R59" t="n">
-        <v>6462900</v>
+        <v>6462748</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6879,10 +6874,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819169</v>
+        <v>123819149</v>
       </c>
       <c r="B60" t="n">
-        <v>79399</v>
+        <v>91008</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6895,21 +6890,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6922,10 +6917,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572447</v>
+        <v>572405</v>
       </c>
       <c r="R60" t="n">
-        <v>6462925</v>
+        <v>6462934</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6985,10 +6980,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819158</v>
+        <v>123819022</v>
       </c>
       <c r="B61" t="n">
-        <v>79399</v>
+        <v>91600</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7001,21 +6996,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572446</v>
+        <v>572325</v>
       </c>
       <c r="R61" t="n">
-        <v>6462925</v>
+        <v>6462706</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7091,10 +7086,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123819121</v>
+        <v>123819130</v>
       </c>
       <c r="B62" t="n">
-        <v>56697</v>
+        <v>79404</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7103,43 +7098,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7147,10 +7129,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572362</v>
+        <v>572378</v>
       </c>
       <c r="R62" t="n">
-        <v>6462874</v>
+        <v>6462897</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7185,17 +7167,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7214,10 +7192,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123818646</v>
+        <v>123818629</v>
       </c>
       <c r="B63" t="n">
-        <v>79399</v>
+        <v>95173</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7226,30 +7204,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7257,10 +7236,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572466</v>
+        <v>572515</v>
       </c>
       <c r="R63" t="n">
-        <v>6462822</v>
+        <v>6462760</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7320,10 +7299,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123819035</v>
+        <v>123818873</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>90972</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7332,25 +7311,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>4660</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7363,10 +7342,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572299</v>
+        <v>572422</v>
       </c>
       <c r="R64" t="n">
-        <v>6462763</v>
+        <v>6462709</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7426,10 +7405,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819149</v>
+        <v>123819073</v>
       </c>
       <c r="B65" t="n">
-        <v>91003</v>
+        <v>78431</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7442,21 +7421,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7469,10 +7448,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572405</v>
+        <v>572257</v>
       </c>
       <c r="R65" t="n">
-        <v>6462934</v>
+        <v>6462806</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7532,10 +7511,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123819022</v>
+        <v>123818682</v>
       </c>
       <c r="B66" t="n">
-        <v>91595</v>
+        <v>57506</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7548,26 +7527,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7575,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572325</v>
+        <v>572441</v>
       </c>
       <c r="R66" t="n">
-        <v>6462706</v>
+        <v>6462802</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7613,13 +7609,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123819089</v>
+        <v>123819034</v>
       </c>
       <c r="B67" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572276</v>
+        <v>572277</v>
       </c>
       <c r="R67" t="n">
-        <v>6462860</v>
+        <v>6462750</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819157</v>
+        <v>123819081</v>
       </c>
       <c r="B2" t="n">
-        <v>78431</v>
+        <v>5479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>101920</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572446</v>
+        <v>572275</v>
       </c>
       <c r="R2" t="n">
-        <v>6462925</v>
+        <v>6462841</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123818639</v>
+        <v>123819088</v>
       </c>
       <c r="B3" t="n">
-        <v>78431</v>
+        <v>78433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572466</v>
+        <v>572276</v>
       </c>
       <c r="R3" t="n">
-        <v>6462822</v>
+        <v>6462860</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819031</v>
+        <v>123818438</v>
       </c>
       <c r="B4" t="n">
-        <v>5492</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,32 +901,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>1110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572284</v>
+        <v>572538</v>
       </c>
       <c r="R4" t="n">
-        <v>6462713</v>
+        <v>6462741</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123818819</v>
+        <v>123818873</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
+        <v>90974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,32 +1007,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101920</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572399</v>
+        <v>572422</v>
       </c>
       <c r="R5" t="n">
-        <v>6462693</v>
+        <v>6462709</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818446</v>
+        <v>123818682</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,31 +1113,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572535</v>
+        <v>572441</v>
       </c>
       <c r="R6" t="n">
-        <v>6462771</v>
+        <v>6462802</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,13 +1199,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818960</v>
+        <v>123818446</v>
       </c>
       <c r="B7" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,39 +1240,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572326</v>
+        <v>572535</v>
       </c>
       <c r="R7" t="n">
-        <v>6462705</v>
+        <v>6462771</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,17 +1310,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123818415</v>
+        <v>123819036</v>
       </c>
       <c r="B8" t="n">
-        <v>95173</v>
+        <v>79406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,31 +1347,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572570</v>
+        <v>572299</v>
       </c>
       <c r="R8" t="n">
-        <v>6462742</v>
+        <v>6462763</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819081</v>
+        <v>123819072</v>
       </c>
       <c r="B9" t="n">
-        <v>5479</v>
+        <v>79406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,32 +1453,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572275</v>
+        <v>572298</v>
       </c>
       <c r="R9" t="n">
-        <v>6462841</v>
+        <v>6462796</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1544,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819088</v>
+        <v>123818843</v>
       </c>
       <c r="B10" t="n">
-        <v>78431</v>
+        <v>78433</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572276</v>
+        <v>572420</v>
       </c>
       <c r="R10" t="n">
-        <v>6462860</v>
+        <v>6462720</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1650,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819082</v>
+        <v>123819035</v>
       </c>
       <c r="B11" t="n">
-        <v>78431</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572275</v>
+        <v>572299</v>
       </c>
       <c r="R11" t="n">
-        <v>6462841</v>
+        <v>6462763</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819167</v>
+        <v>123819084</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>79406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572447</v>
+        <v>572275</v>
       </c>
       <c r="R12" t="n">
-        <v>6462925</v>
+        <v>6462841</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819032</v>
+        <v>123819096</v>
       </c>
       <c r="B13" t="n">
-        <v>79404</v>
+        <v>91010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572284</v>
+        <v>572307</v>
       </c>
       <c r="R13" t="n">
-        <v>6462713</v>
+        <v>6462856</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123819096</v>
+        <v>123818454</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,30 +1983,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572307</v>
+        <v>572542</v>
       </c>
       <c r="R14" t="n">
-        <v>6462856</v>
+        <v>6462761</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818763</v>
+        <v>123818966</v>
       </c>
       <c r="B15" t="n">
-        <v>90986</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,30 +2090,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572392</v>
+        <v>572304</v>
       </c>
       <c r="R15" t="n">
-        <v>6462722</v>
+        <v>6462690</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2180,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123819172</v>
+        <v>123818763</v>
       </c>
       <c r="B16" t="n">
-        <v>90986</v>
+        <v>90988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572456</v>
+        <v>572392</v>
       </c>
       <c r="R16" t="n">
-        <v>6462900</v>
+        <v>6462722</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2286,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123818454</v>
+        <v>123818426</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,31 +2303,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2330,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572542</v>
+        <v>572545</v>
       </c>
       <c r="R17" t="n">
-        <v>6462761</v>
+        <v>6462716</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2393,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123818742</v>
+        <v>123819158</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,31 +2409,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2437,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572433</v>
+        <v>572446</v>
       </c>
       <c r="R18" t="n">
-        <v>6462777</v>
+        <v>6462925</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2500,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819162</v>
+        <v>123819032</v>
       </c>
       <c r="B19" t="n">
-        <v>78431</v>
+        <v>79406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572447</v>
+        <v>572284</v>
       </c>
       <c r="R19" t="n">
-        <v>6462925</v>
+        <v>6462713</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2606,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818331</v>
+        <v>123819098</v>
       </c>
       <c r="B20" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2649,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572576</v>
+        <v>572307</v>
       </c>
       <c r="R20" t="n">
-        <v>6462698</v>
+        <v>6462856</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2712,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123818938</v>
+        <v>123818542</v>
       </c>
       <c r="B21" t="n">
-        <v>74817</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,30 +2727,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2755,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572347</v>
+        <v>572542</v>
       </c>
       <c r="R21" t="n">
-        <v>6462723</v>
+        <v>6462761</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,7 +2807,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2818,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818643</v>
+        <v>123818960</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,26 +2841,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2861,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572466</v>
+        <v>572326</v>
       </c>
       <c r="R22" t="n">
-        <v>6462822</v>
+        <v>6462705</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2899,13 +2915,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2924,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819084</v>
+        <v>123819025</v>
       </c>
       <c r="B23" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,30 +2956,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2967,10 +2988,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572275</v>
+        <v>572337</v>
       </c>
       <c r="R23" t="n">
-        <v>6462841</v>
+        <v>6462716</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3030,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123818426</v>
+        <v>123819162</v>
       </c>
       <c r="B24" t="n">
-        <v>92269</v>
+        <v>78433</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,25 +3063,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572545</v>
+        <v>572447</v>
       </c>
       <c r="R24" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3136,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819036</v>
+        <v>123819077</v>
       </c>
       <c r="B25" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3152,21 +3173,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572299</v>
+        <v>572247</v>
       </c>
       <c r="R25" t="n">
-        <v>6462763</v>
+        <v>6462824</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3242,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123818837</v>
+        <v>123818643</v>
       </c>
       <c r="B26" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3285,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572414</v>
+        <v>572466</v>
       </c>
       <c r="R26" t="n">
-        <v>6462716</v>
+        <v>6462822</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3348,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123818843</v>
+        <v>123818331</v>
       </c>
       <c r="B27" t="n">
-        <v>78431</v>
+        <v>79406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,21 +3385,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572420</v>
+        <v>572576</v>
       </c>
       <c r="R27" t="n">
-        <v>6462720</v>
+        <v>6462698</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,10 +3475,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818916</v>
+        <v>123819124</v>
       </c>
       <c r="B28" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572384</v>
+        <v>572362</v>
       </c>
       <c r="R28" t="n">
-        <v>6462675</v>
+        <v>6462874</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3560,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818852</v>
+        <v>123818938</v>
       </c>
       <c r="B29" t="n">
-        <v>79404</v>
+        <v>74818</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3572,25 +3593,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572410</v>
+        <v>572347</v>
       </c>
       <c r="R29" t="n">
-        <v>6462725</v>
+        <v>6462723</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3666,10 +3687,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819035</v>
+        <v>123819169</v>
       </c>
       <c r="B30" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3703,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3730,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572299</v>
+        <v>572447</v>
       </c>
       <c r="R30" t="n">
-        <v>6462763</v>
+        <v>6462925</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3775,7 +3796,7 @@
         <v>123818753</v>
       </c>
       <c r="B31" t="n">
-        <v>78431</v>
+        <v>78433</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3878,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123818411</v>
+        <v>123818415</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,25 +3911,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3985,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819158</v>
+        <v>123819082</v>
       </c>
       <c r="B33" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4001,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4028,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572446</v>
+        <v>572275</v>
       </c>
       <c r="R33" t="n">
-        <v>6462925</v>
+        <v>6462841</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4091,10 +4112,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819177</v>
+        <v>123819172</v>
       </c>
       <c r="B34" t="n">
-        <v>79404</v>
+        <v>90988</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4103,25 +4124,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4197,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819098</v>
+        <v>123819074</v>
       </c>
       <c r="B35" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572307</v>
+        <v>572257</v>
       </c>
       <c r="R35" t="n">
-        <v>6462856</v>
+        <v>6462806</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4303,10 +4324,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123818871</v>
+        <v>123818819</v>
       </c>
       <c r="B36" t="n">
-        <v>5492</v>
+        <v>5479</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,25 +4336,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101410</v>
+        <v>101920</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4369,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572422</v>
+        <v>572399</v>
       </c>
       <c r="R36" t="n">
-        <v>6462709</v>
+        <v>6462693</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4411,10 +4432,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123818345</v>
+        <v>123819177</v>
       </c>
       <c r="B37" t="n">
-        <v>95173</v>
+        <v>79406</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4423,31 +4444,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4455,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572575</v>
+        <v>572456</v>
       </c>
       <c r="R37" t="n">
-        <v>6462706</v>
+        <v>6462900</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4518,10 +4538,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123818388</v>
+        <v>123818629</v>
       </c>
       <c r="B38" t="n">
-        <v>79404</v>
+        <v>95175</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4530,30 +4550,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4561,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572560</v>
+        <v>572515</v>
       </c>
       <c r="R38" t="n">
-        <v>6462694</v>
+        <v>6462760</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4624,10 +4645,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819173</v>
+        <v>123819089</v>
       </c>
       <c r="B39" t="n">
-        <v>92304</v>
+        <v>79406</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4640,21 +4661,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572456</v>
+        <v>572276</v>
       </c>
       <c r="R39" t="n">
-        <v>6462900</v>
+        <v>6462860</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4730,10 +4751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123819077</v>
+        <v>123818852</v>
       </c>
       <c r="B40" t="n">
-        <v>78431</v>
+        <v>79406</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4746,21 +4767,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4773,10 +4794,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572247</v>
+        <v>572410</v>
       </c>
       <c r="R40" t="n">
-        <v>6462824</v>
+        <v>6462725</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4836,10 +4857,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123819179</v>
+        <v>123818742</v>
       </c>
       <c r="B41" t="n">
-        <v>78431</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4848,30 +4869,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4879,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572456</v>
+        <v>572433</v>
       </c>
       <c r="R41" t="n">
-        <v>6462900</v>
+        <v>6462777</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4942,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123818360</v>
+        <v>123819073</v>
       </c>
       <c r="B42" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4958,21 +4980,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4985,10 +5007,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572567</v>
+        <v>572257</v>
       </c>
       <c r="R42" t="n">
-        <v>6462723</v>
+        <v>6462806</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5048,10 +5070,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819072</v>
+        <v>123819179</v>
       </c>
       <c r="B43" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5064,21 +5086,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5091,10 +5113,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572298</v>
+        <v>572456</v>
       </c>
       <c r="R43" t="n">
-        <v>6462796</v>
+        <v>6462900</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5154,10 +5176,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818966</v>
+        <v>123818646</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5166,31 +5188,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5198,10 +5219,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572304</v>
+        <v>572466</v>
       </c>
       <c r="R44" t="n">
-        <v>6462690</v>
+        <v>6462822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5261,10 +5282,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818542</v>
+        <v>123818936</v>
       </c>
       <c r="B45" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5273,35 +5294,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5309,10 +5326,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572542</v>
+        <v>572347</v>
       </c>
       <c r="R45" t="n">
-        <v>6462761</v>
+        <v>6462723</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5353,6 +5370,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5371,10 +5389,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819121</v>
+        <v>123819167</v>
       </c>
       <c r="B46" t="n">
-        <v>56700</v>
+        <v>91010</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,43 +5401,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5427,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572362</v>
+        <v>572447</v>
       </c>
       <c r="R46" t="n">
-        <v>6462874</v>
+        <v>6462925</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5465,17 +5470,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5494,10 +5495,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123818381</v>
+        <v>123819149</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5537,10 +5538,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572568</v>
+        <v>572405</v>
       </c>
       <c r="R47" t="n">
-        <v>6462684</v>
+        <v>6462934</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5600,10 +5601,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818438</v>
+        <v>123818381</v>
       </c>
       <c r="B48" t="n">
-        <v>90986</v>
+        <v>91010</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5612,25 +5613,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1110</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5643,10 +5644,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572538</v>
+        <v>572568</v>
       </c>
       <c r="R48" t="n">
-        <v>6462741</v>
+        <v>6462684</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5706,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818936</v>
+        <v>123818360</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5718,31 +5719,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572347</v>
+        <v>572567</v>
       </c>
       <c r="R49" t="n">
         <v>6462723</v>
@@ -5813,10 +5813,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123819089</v>
+        <v>123818871</v>
       </c>
       <c r="B50" t="n">
-        <v>79404</v>
+        <v>5492</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5829,26 +5829,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5856,10 +5858,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572276</v>
+        <v>572422</v>
       </c>
       <c r="R50" t="n">
-        <v>6462860</v>
+        <v>6462709</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5919,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123819025</v>
+        <v>123819157</v>
       </c>
       <c r="B51" t="n">
-        <v>98502</v>
+        <v>78433</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5931,31 +5933,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5963,10 +5964,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572337</v>
+        <v>572446</v>
       </c>
       <c r="R51" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6026,10 +6027,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123818646</v>
+        <v>123819173</v>
       </c>
       <c r="B52" t="n">
-        <v>79404</v>
+        <v>92306</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6042,21 +6043,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6069,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572466</v>
+        <v>572456</v>
       </c>
       <c r="R52" t="n">
-        <v>6462822</v>
+        <v>6462900</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6132,10 +6133,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123819074</v>
+        <v>123818916</v>
       </c>
       <c r="B53" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,10 +6176,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572257</v>
+        <v>572384</v>
       </c>
       <c r="R53" t="n">
-        <v>6462806</v>
+        <v>6462675</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6238,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123819176</v>
+        <v>123819031</v>
       </c>
       <c r="B54" t="n">
-        <v>91008</v>
+        <v>5492</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6254,26 +6255,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6281,10 +6284,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572456</v>
+        <v>572284</v>
       </c>
       <c r="R54" t="n">
-        <v>6462900</v>
+        <v>6462713</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6344,10 +6347,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123818826</v>
+        <v>123818345</v>
       </c>
       <c r="B55" t="n">
-        <v>79404</v>
+        <v>95175</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6356,30 +6359,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6387,10 +6391,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572399</v>
+        <v>572575</v>
       </c>
       <c r="R55" t="n">
-        <v>6462693</v>
+        <v>6462706</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6450,10 +6454,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818757</v>
+        <v>123818388</v>
       </c>
       <c r="B56" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6493,10 +6497,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572407</v>
+        <v>572560</v>
       </c>
       <c r="R56" t="n">
-        <v>6462746</v>
+        <v>6462694</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6556,10 +6560,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123819169</v>
+        <v>123819176</v>
       </c>
       <c r="B57" t="n">
-        <v>79404</v>
+        <v>91010</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6572,21 +6576,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6599,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572447</v>
+        <v>572456</v>
       </c>
       <c r="R57" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6662,10 +6666,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123819124</v>
+        <v>123818837</v>
       </c>
       <c r="B58" t="n">
-        <v>79404</v>
+        <v>91010</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6678,21 +6682,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6705,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572362</v>
+        <v>572414</v>
       </c>
       <c r="R58" t="n">
-        <v>6462874</v>
+        <v>6462716</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6768,10 +6772,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123818590</v>
+        <v>123819121</v>
       </c>
       <c r="B59" t="n">
-        <v>79404</v>
+        <v>56700</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6780,30 +6784,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6811,10 +6828,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572563</v>
+        <v>572362</v>
       </c>
       <c r="R59" t="n">
-        <v>6462748</v>
+        <v>6462874</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6849,13 +6866,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6874,10 +6895,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819149</v>
+        <v>123818411</v>
       </c>
       <c r="B60" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6886,30 +6907,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6917,10 +6939,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572405</v>
+        <v>572570</v>
       </c>
       <c r="R60" t="n">
-        <v>6462934</v>
+        <v>6462742</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6980,10 +7002,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819022</v>
+        <v>123818639</v>
       </c>
       <c r="B61" t="n">
-        <v>91600</v>
+        <v>78433</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6996,21 +7018,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5454</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7023,10 +7045,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572325</v>
+        <v>572466</v>
       </c>
       <c r="R61" t="n">
-        <v>6462706</v>
+        <v>6462822</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7086,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123819130</v>
+        <v>123819034</v>
       </c>
       <c r="B62" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7129,10 +7151,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572378</v>
+        <v>572277</v>
       </c>
       <c r="R62" t="n">
-        <v>6462897</v>
+        <v>6462750</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7192,10 +7214,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123818629</v>
+        <v>123819130</v>
       </c>
       <c r="B63" t="n">
-        <v>95173</v>
+        <v>79406</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7204,31 +7226,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7236,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572515</v>
+        <v>572378</v>
       </c>
       <c r="R63" t="n">
-        <v>6462760</v>
+        <v>6462897</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7299,10 +7320,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818873</v>
+        <v>123818826</v>
       </c>
       <c r="B64" t="n">
-        <v>90972</v>
+        <v>79406</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7311,25 +7332,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7342,10 +7363,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572422</v>
+        <v>572399</v>
       </c>
       <c r="R64" t="n">
-        <v>6462709</v>
+        <v>6462693</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7405,10 +7426,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819073</v>
+        <v>123818590</v>
       </c>
       <c r="B65" t="n">
-        <v>78431</v>
+        <v>79406</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7421,21 +7442,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7448,10 +7469,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572257</v>
+        <v>572563</v>
       </c>
       <c r="R65" t="n">
-        <v>6462806</v>
+        <v>6462748</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7511,10 +7532,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818682</v>
+        <v>123818757</v>
       </c>
       <c r="B66" t="n">
-        <v>57506</v>
+        <v>79406</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7527,43 +7548,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7571,10 +7575,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572441</v>
+        <v>572407</v>
       </c>
       <c r="R66" t="n">
-        <v>6462802</v>
+        <v>6462746</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7609,17 +7613,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123819034</v>
+        <v>123819022</v>
       </c>
       <c r="B67" t="n">
-        <v>79404</v>
+        <v>91602</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7654,21 +7654,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572277</v>
+        <v>572325</v>
       </c>
       <c r="R67" t="n">
-        <v>6462750</v>
+        <v>6462706</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -3475,10 +3475,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123819124</v>
+        <v>123818753</v>
       </c>
       <c r="B28" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572362</v>
+        <v>572414</v>
       </c>
       <c r="R28" t="n">
-        <v>6462874</v>
+        <v>6462768</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818938</v>
+        <v>123818415</v>
       </c>
       <c r="B29" t="n">
-        <v>74818</v>
+        <v>95175</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3597,26 +3597,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3624,10 +3625,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572347</v>
+        <v>572570</v>
       </c>
       <c r="R29" t="n">
-        <v>6462723</v>
+        <v>6462742</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3687,7 +3688,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819169</v>
+        <v>123819124</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3730,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572447</v>
+        <v>572362</v>
       </c>
       <c r="R30" t="n">
-        <v>6462925</v>
+        <v>6462874</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3793,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818753</v>
+        <v>123818938</v>
       </c>
       <c r="B31" t="n">
-        <v>78433</v>
+        <v>74818</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3805,25 +3806,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3837,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572414</v>
+        <v>572347</v>
       </c>
       <c r="R31" t="n">
-        <v>6462768</v>
+        <v>6462723</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123818415</v>
+        <v>123819169</v>
       </c>
       <c r="B32" t="n">
-        <v>95175</v>
+        <v>79406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,31 +3912,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572570</v>
+        <v>572447</v>
       </c>
       <c r="R32" t="n">
-        <v>6462742</v>
+        <v>6462925</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5282,10 +5282,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818936</v>
+        <v>123819167</v>
       </c>
       <c r="B45" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5294,31 +5294,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5326,10 +5325,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572347</v>
+        <v>572447</v>
       </c>
       <c r="R45" t="n">
-        <v>6462723</v>
+        <v>6462925</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5389,7 +5388,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819167</v>
+        <v>123819149</v>
       </c>
       <c r="B46" t="n">
         <v>91010</v>
@@ -5432,10 +5431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572447</v>
+        <v>572405</v>
       </c>
       <c r="R46" t="n">
-        <v>6462925</v>
+        <v>6462934</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5495,7 +5494,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819149</v>
+        <v>123818381</v>
       </c>
       <c r="B47" t="n">
         <v>91010</v>
@@ -5538,10 +5537,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572405</v>
+        <v>572568</v>
       </c>
       <c r="R47" t="n">
-        <v>6462934</v>
+        <v>6462684</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5601,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818381</v>
+        <v>123818936</v>
       </c>
       <c r="B48" t="n">
-        <v>91010</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5613,30 +5612,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572568</v>
+        <v>572347</v>
       </c>
       <c r="R48" t="n">
-        <v>6462684</v>
+        <v>6462723</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818360</v>
+        <v>123818871</v>
       </c>
       <c r="B49" t="n">
-        <v>79406</v>
+        <v>5492</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5723,26 +5723,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5750,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572567</v>
+        <v>572422</v>
       </c>
       <c r="R49" t="n">
-        <v>6462723</v>
+        <v>6462709</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5813,10 +5815,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818871</v>
+        <v>123818360</v>
       </c>
       <c r="B50" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5829,28 +5831,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572422</v>
+        <v>572567</v>
       </c>
       <c r="R50" t="n">
-        <v>6462709</v>
+        <v>6462723</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -5707,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818871</v>
+        <v>123818360</v>
       </c>
       <c r="B49" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5723,28 +5723,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5752,10 +5750,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572422</v>
+        <v>572567</v>
       </c>
       <c r="R49" t="n">
-        <v>6462709</v>
+        <v>6462723</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5815,10 +5813,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818360</v>
+        <v>123818871</v>
       </c>
       <c r="B50" t="n">
-        <v>79406</v>
+        <v>5492</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5831,26 +5829,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572567</v>
+        <v>572422</v>
       </c>
       <c r="R50" t="n">
-        <v>6462723</v>
+        <v>6462709</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123819031</v>
+        <v>123818345</v>
       </c>
       <c r="B54" t="n">
-        <v>5492</v>
+        <v>95175</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6251,32 +6251,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6284,10 +6283,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572284</v>
+        <v>572575</v>
       </c>
       <c r="R54" t="n">
-        <v>6462713</v>
+        <v>6462706</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6347,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123818345</v>
+        <v>123818388</v>
       </c>
       <c r="B55" t="n">
-        <v>95175</v>
+        <v>79406</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6359,31 +6358,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6391,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572575</v>
+        <v>572560</v>
       </c>
       <c r="R55" t="n">
-        <v>6462706</v>
+        <v>6462694</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6454,10 +6452,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818388</v>
+        <v>123819176</v>
       </c>
       <c r="B56" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6470,21 +6468,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6497,10 +6495,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572560</v>
+        <v>572456</v>
       </c>
       <c r="R56" t="n">
-        <v>6462694</v>
+        <v>6462900</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6560,7 +6558,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123819176</v>
+        <v>123818837</v>
       </c>
       <c r="B57" t="n">
         <v>91010</v>
@@ -6603,10 +6601,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572456</v>
+        <v>572414</v>
       </c>
       <c r="R57" t="n">
-        <v>6462900</v>
+        <v>6462716</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6666,10 +6664,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818837</v>
+        <v>123819031</v>
       </c>
       <c r="B58" t="n">
-        <v>91010</v>
+        <v>5492</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6682,26 +6680,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572414</v>
+        <v>572284</v>
       </c>
       <c r="R58" t="n">
-        <v>6462716</v>
+        <v>6462713</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819081</v>
+        <v>123819034</v>
       </c>
       <c r="B2" t="n">
-        <v>5479</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572275</v>
+        <v>572277</v>
       </c>
       <c r="R2" t="n">
-        <v>6462841</v>
+        <v>6462750</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -783,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819088</v>
+        <v>123819036</v>
       </c>
       <c r="B3" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572276</v>
+        <v>572299</v>
       </c>
       <c r="R3" t="n">
-        <v>6462860</v>
+        <v>6462763</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123818438</v>
+        <v>123819124</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572538</v>
+        <v>572362</v>
       </c>
       <c r="R4" t="n">
-        <v>6462741</v>
+        <v>6462874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123818873</v>
+        <v>123819088</v>
       </c>
       <c r="B5" t="n">
-        <v>90974</v>
+        <v>78433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572422</v>
+        <v>572276</v>
       </c>
       <c r="R5" t="n">
-        <v>6462709</v>
+        <v>6462860</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818682</v>
+        <v>123818438</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,47 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572441</v>
+        <v>572538</v>
       </c>
       <c r="R6" t="n">
-        <v>6462802</v>
+        <v>6462741</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,17 +1180,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1228,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818446</v>
+        <v>123818753</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,31 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1272,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572535</v>
+        <v>572414</v>
       </c>
       <c r="R7" t="n">
-        <v>6462771</v>
+        <v>6462768</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819036</v>
+        <v>123818871</v>
       </c>
       <c r="B8" t="n">
-        <v>79406</v>
+        <v>5492</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,26 +1327,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572299</v>
+        <v>572422</v>
       </c>
       <c r="R8" t="n">
-        <v>6462763</v>
+        <v>6462709</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1441,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819072</v>
+        <v>123818381</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572298</v>
+        <v>572568</v>
       </c>
       <c r="R9" t="n">
-        <v>6462796</v>
+        <v>6462684</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818843</v>
+        <v>123819169</v>
       </c>
       <c r="B10" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572420</v>
+        <v>572447</v>
       </c>
       <c r="R10" t="n">
-        <v>6462720</v>
+        <v>6462925</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819035</v>
+        <v>123818843</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>78433</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572299</v>
+        <v>572420</v>
       </c>
       <c r="R11" t="n">
-        <v>6462763</v>
+        <v>6462720</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1759,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819084</v>
+        <v>123819077</v>
       </c>
       <c r="B12" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572275</v>
+        <v>572247</v>
       </c>
       <c r="R12" t="n">
-        <v>6462841</v>
+        <v>6462824</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819096</v>
+        <v>123819173</v>
       </c>
       <c r="B13" t="n">
-        <v>91010</v>
+        <v>92306</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572307</v>
+        <v>572456</v>
       </c>
       <c r="R13" t="n">
-        <v>6462856</v>
+        <v>6462900</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1971,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818454</v>
+        <v>123819096</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,31 +1961,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2015,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572542</v>
+        <v>572307</v>
       </c>
       <c r="R14" t="n">
-        <v>6462761</v>
+        <v>6462856</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818966</v>
+        <v>123818646</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,31 +2067,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2122,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572304</v>
+        <v>572466</v>
       </c>
       <c r="R15" t="n">
-        <v>6462690</v>
+        <v>6462822</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2185,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818763</v>
+        <v>123819022</v>
       </c>
       <c r="B16" t="n">
-        <v>90988</v>
+        <v>91602</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,25 +2173,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1110</v>
+        <v>5454</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572392</v>
+        <v>572325</v>
       </c>
       <c r="R16" t="n">
-        <v>6462722</v>
+        <v>6462706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2291,10 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123818426</v>
+        <v>123819121</v>
       </c>
       <c r="B17" t="n">
-        <v>92271</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,26 +2283,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2334,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572545</v>
+        <v>572362</v>
       </c>
       <c r="R17" t="n">
-        <v>6462716</v>
+        <v>6462874</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,13 +2361,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2397,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819158</v>
+        <v>123818742</v>
       </c>
       <c r="B18" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,30 +2402,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2440,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572446</v>
+        <v>572433</v>
       </c>
       <c r="R18" t="n">
-        <v>6462925</v>
+        <v>6462777</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2503,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819032</v>
+        <v>123818966</v>
       </c>
       <c r="B19" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,30 +2509,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2546,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572284</v>
+        <v>572304</v>
       </c>
       <c r="R19" t="n">
-        <v>6462713</v>
+        <v>6462690</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819098</v>
+        <v>123818763</v>
       </c>
       <c r="B20" t="n">
-        <v>79406</v>
+        <v>90988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2616,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572307</v>
+        <v>572392</v>
       </c>
       <c r="R20" t="n">
-        <v>6462856</v>
+        <v>6462722</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,10 +2710,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123818542</v>
+        <v>123818345</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,35 +2722,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572542</v>
+        <v>572575</v>
       </c>
       <c r="R21" t="n">
-        <v>6462761</v>
+        <v>6462706</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2807,6 +2798,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2825,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818960</v>
+        <v>123819158</v>
       </c>
       <c r="B22" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,35 +2833,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2877,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572326</v>
+        <v>572446</v>
       </c>
       <c r="R22" t="n">
-        <v>6462705</v>
+        <v>6462925</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,17 +2898,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2944,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819025</v>
+        <v>123819149</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,31 +2935,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2988,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572337</v>
+        <v>572405</v>
       </c>
       <c r="R23" t="n">
-        <v>6462716</v>
+        <v>6462934</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3051,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819162</v>
+        <v>123819176</v>
       </c>
       <c r="B24" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3094,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572447</v>
+        <v>572456</v>
       </c>
       <c r="R24" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3157,10 +3135,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819077</v>
+        <v>123818643</v>
       </c>
       <c r="B25" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,21 +3151,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3200,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572247</v>
+        <v>572466</v>
       </c>
       <c r="R25" t="n">
-        <v>6462824</v>
+        <v>6462822</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3263,10 +3241,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123818643</v>
+        <v>123818590</v>
       </c>
       <c r="B26" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3279,21 +3257,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3306,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572466</v>
+        <v>572563</v>
       </c>
       <c r="R26" t="n">
-        <v>6462822</v>
+        <v>6462748</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3369,7 +3347,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123818331</v>
+        <v>123819032</v>
       </c>
       <c r="B27" t="n">
         <v>79406</v>
@@ -3412,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572576</v>
+        <v>572284</v>
       </c>
       <c r="R27" t="n">
-        <v>6462698</v>
+        <v>6462713</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3475,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818753</v>
+        <v>123818454</v>
       </c>
       <c r="B28" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3487,30 +3465,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3518,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572414</v>
+        <v>572542</v>
       </c>
       <c r="R28" t="n">
-        <v>6462768</v>
+        <v>6462761</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3581,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818415</v>
+        <v>123819084</v>
       </c>
       <c r="B29" t="n">
-        <v>95175</v>
+        <v>79406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,31 +3572,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3625,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572570</v>
+        <v>572275</v>
       </c>
       <c r="R29" t="n">
-        <v>6462742</v>
+        <v>6462841</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3688,7 +3666,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819124</v>
+        <v>123819089</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3731,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572362</v>
+        <v>572276</v>
       </c>
       <c r="R30" t="n">
-        <v>6462874</v>
+        <v>6462860</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3794,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818938</v>
+        <v>123818852</v>
       </c>
       <c r="B31" t="n">
-        <v>74818</v>
+        <v>79406</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,25 +3784,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3837,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572347</v>
+        <v>572410</v>
       </c>
       <c r="R31" t="n">
-        <v>6462723</v>
+        <v>6462725</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3900,7 +3878,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819169</v>
+        <v>123819072</v>
       </c>
       <c r="B32" t="n">
         <v>79406</v>
@@ -3943,10 +3921,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572447</v>
+        <v>572298</v>
       </c>
       <c r="R32" t="n">
-        <v>6462925</v>
+        <v>6462796</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4006,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819082</v>
+        <v>123818873</v>
       </c>
       <c r="B33" t="n">
-        <v>78433</v>
+        <v>90974</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4018,25 +3996,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4660</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4049,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572275</v>
+        <v>572422</v>
       </c>
       <c r="R33" t="n">
-        <v>6462841</v>
+        <v>6462709</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4112,10 +4090,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819172</v>
+        <v>123819081</v>
       </c>
       <c r="B34" t="n">
-        <v>90988</v>
+        <v>5479</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4124,30 +4102,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1110</v>
+        <v>101920</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4155,10 +4135,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572456</v>
+        <v>572275</v>
       </c>
       <c r="R34" t="n">
-        <v>6462900</v>
+        <v>6462841</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4218,10 +4198,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819074</v>
+        <v>123818819</v>
       </c>
       <c r="B35" t="n">
-        <v>79406</v>
+        <v>5479</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4230,30 +4210,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4261,10 +4243,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572257</v>
+        <v>572399</v>
       </c>
       <c r="R35" t="n">
-        <v>6462806</v>
+        <v>6462693</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4324,10 +4306,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123818819</v>
+        <v>123818938</v>
       </c>
       <c r="B36" t="n">
-        <v>5479</v>
+        <v>74818</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4336,32 +4318,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101920</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4369,10 +4349,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572399</v>
+        <v>572347</v>
       </c>
       <c r="R36" t="n">
-        <v>6462693</v>
+        <v>6462723</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4432,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819177</v>
+        <v>123819073</v>
       </c>
       <c r="B37" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4448,21 +4428,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572456</v>
+        <v>572257</v>
       </c>
       <c r="R37" t="n">
-        <v>6462900</v>
+        <v>6462806</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4538,10 +4518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123818629</v>
+        <v>123819179</v>
       </c>
       <c r="B38" t="n">
-        <v>95175</v>
+        <v>78433</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4550,31 +4530,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4582,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572515</v>
+        <v>572456</v>
       </c>
       <c r="R38" t="n">
-        <v>6462760</v>
+        <v>6462900</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4645,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819089</v>
+        <v>123819167</v>
       </c>
       <c r="B39" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4661,21 +4640,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572276</v>
+        <v>572447</v>
       </c>
       <c r="R39" t="n">
-        <v>6462860</v>
+        <v>6462925</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4751,10 +4730,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818852</v>
+        <v>123818936</v>
       </c>
       <c r="B40" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4763,30 +4742,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4794,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572410</v>
+        <v>572347</v>
       </c>
       <c r="R40" t="n">
-        <v>6462725</v>
+        <v>6462723</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4857,10 +4837,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818742</v>
+        <v>123818360</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4869,31 +4849,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4901,10 +4880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572433</v>
+        <v>572567</v>
       </c>
       <c r="R41" t="n">
-        <v>6462777</v>
+        <v>6462723</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4964,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819073</v>
+        <v>123819130</v>
       </c>
       <c r="B42" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4980,21 +4959,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5007,10 +4986,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572257</v>
+        <v>572378</v>
       </c>
       <c r="R42" t="n">
-        <v>6462806</v>
+        <v>6462897</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5070,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819179</v>
+        <v>123818629</v>
       </c>
       <c r="B43" t="n">
-        <v>78433</v>
+        <v>95683</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5082,30 +5061,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5113,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572456</v>
+        <v>572515</v>
       </c>
       <c r="R43" t="n">
-        <v>6462900</v>
+        <v>6462760</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5176,10 +5156,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818646</v>
+        <v>123818426</v>
       </c>
       <c r="B44" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5188,25 +5168,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5219,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572466</v>
+        <v>572545</v>
       </c>
       <c r="R44" t="n">
-        <v>6462822</v>
+        <v>6462716</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,10 +5262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123819167</v>
+        <v>123818826</v>
       </c>
       <c r="B45" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5298,21 +5278,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5325,10 +5305,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572447</v>
+        <v>572399</v>
       </c>
       <c r="R45" t="n">
-        <v>6462925</v>
+        <v>6462693</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5388,10 +5368,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819149</v>
+        <v>123818331</v>
       </c>
       <c r="B46" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5404,21 +5384,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5431,10 +5411,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572405</v>
+        <v>572576</v>
       </c>
       <c r="R46" t="n">
-        <v>6462934</v>
+        <v>6462698</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5494,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123818381</v>
+        <v>123819162</v>
       </c>
       <c r="B47" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5510,21 +5490,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5537,10 +5517,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572568</v>
+        <v>572447</v>
       </c>
       <c r="R47" t="n">
-        <v>6462684</v>
+        <v>6462925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5600,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818936</v>
+        <v>123818639</v>
       </c>
       <c r="B48" t="n">
-        <v>98504</v>
+        <v>78433</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5612,31 +5592,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5644,10 +5623,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572347</v>
+        <v>572466</v>
       </c>
       <c r="R48" t="n">
-        <v>6462723</v>
+        <v>6462822</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5707,10 +5686,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818360</v>
+        <v>123819025</v>
       </c>
       <c r="B49" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5719,30 +5698,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5750,10 +5730,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572567</v>
+        <v>572337</v>
       </c>
       <c r="R49" t="n">
-        <v>6462723</v>
+        <v>6462716</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5813,10 +5793,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818871</v>
+        <v>123818446</v>
       </c>
       <c r="B50" t="n">
-        <v>5492</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5825,32 +5805,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5858,10 +5837,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572422</v>
+        <v>572535</v>
       </c>
       <c r="R50" t="n">
-        <v>6462709</v>
+        <v>6462771</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5921,10 +5900,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123819157</v>
+        <v>123818916</v>
       </c>
       <c r="B51" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5937,21 +5916,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5964,10 +5943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572446</v>
+        <v>572384</v>
       </c>
       <c r="R51" t="n">
-        <v>6462925</v>
+        <v>6462675</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6027,10 +6006,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123819173</v>
+        <v>123818757</v>
       </c>
       <c r="B52" t="n">
-        <v>92306</v>
+        <v>79406</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6043,21 +6022,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6070,10 +6049,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572456</v>
+        <v>572407</v>
       </c>
       <c r="R52" t="n">
-        <v>6462900</v>
+        <v>6462746</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6133,10 +6112,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818916</v>
+        <v>123819157</v>
       </c>
       <c r="B53" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6149,21 +6128,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6176,10 +6155,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572384</v>
+        <v>572446</v>
       </c>
       <c r="R53" t="n">
-        <v>6462675</v>
+        <v>6462925</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6239,10 +6218,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818345</v>
+        <v>123819172</v>
       </c>
       <c r="B54" t="n">
-        <v>95175</v>
+        <v>90988</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6251,31 +6230,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2180</v>
+        <v>1110</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6283,10 +6261,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572575</v>
+        <v>572456</v>
       </c>
       <c r="R54" t="n">
-        <v>6462706</v>
+        <v>6462900</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6346,10 +6324,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123818388</v>
+        <v>123819031</v>
       </c>
       <c r="B55" t="n">
-        <v>79406</v>
+        <v>5492</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6362,26 +6340,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6389,10 +6369,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572560</v>
+        <v>572284</v>
       </c>
       <c r="R55" t="n">
-        <v>6462694</v>
+        <v>6462713</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6452,10 +6432,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123819176</v>
+        <v>123819074</v>
       </c>
       <c r="B56" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6468,21 +6448,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6495,10 +6475,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572456</v>
+        <v>572257</v>
       </c>
       <c r="R56" t="n">
-        <v>6462900</v>
+        <v>6462806</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6558,10 +6538,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818837</v>
+        <v>123818388</v>
       </c>
       <c r="B57" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6574,21 +6554,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6601,10 +6581,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572414</v>
+        <v>572560</v>
       </c>
       <c r="R57" t="n">
-        <v>6462716</v>
+        <v>6462694</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6664,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123819031</v>
+        <v>123818411</v>
       </c>
       <c r="B58" t="n">
-        <v>5492</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6676,32 +6656,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6709,10 +6688,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572284</v>
+        <v>572570</v>
       </c>
       <c r="R58" t="n">
-        <v>6462713</v>
+        <v>6462742</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6772,10 +6751,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819121</v>
+        <v>123819082</v>
       </c>
       <c r="B59" t="n">
-        <v>56700</v>
+        <v>78433</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6784,43 +6763,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6828,10 +6794,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572362</v>
+        <v>572275</v>
       </c>
       <c r="R59" t="n">
-        <v>6462874</v>
+        <v>6462841</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6866,17 +6832,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6895,10 +6857,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123818411</v>
+        <v>123819035</v>
       </c>
       <c r="B60" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6907,31 +6869,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6939,10 +6900,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572570</v>
+        <v>572299</v>
       </c>
       <c r="R60" t="n">
-        <v>6462742</v>
+        <v>6462763</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7002,10 +6963,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123818639</v>
+        <v>123818415</v>
       </c>
       <c r="B61" t="n">
-        <v>78433</v>
+        <v>95683</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7014,30 +6975,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7045,10 +7007,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572466</v>
+        <v>572570</v>
       </c>
       <c r="R61" t="n">
-        <v>6462822</v>
+        <v>6462742</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7108,7 +7070,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123819034</v>
+        <v>123819177</v>
       </c>
       <c r="B62" t="n">
         <v>79406</v>
@@ -7151,10 +7113,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572277</v>
+        <v>572456</v>
       </c>
       <c r="R62" t="n">
-        <v>6462750</v>
+        <v>6462900</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7214,7 +7176,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819130</v>
+        <v>123819098</v>
       </c>
       <c r="B63" t="n">
         <v>79406</v>
@@ -7257,10 +7219,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572378</v>
+        <v>572307</v>
       </c>
       <c r="R63" t="n">
-        <v>6462897</v>
+        <v>6462856</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7320,10 +7282,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818826</v>
+        <v>123818837</v>
       </c>
       <c r="B64" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7336,21 +7298,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7363,10 +7325,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572399</v>
+        <v>572414</v>
       </c>
       <c r="R64" t="n">
-        <v>6462693</v>
+        <v>6462716</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7426,10 +7388,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123818590</v>
+        <v>123818960</v>
       </c>
       <c r="B65" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7442,26 +7404,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7469,10 +7440,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572563</v>
+        <v>572326</v>
       </c>
       <c r="R65" t="n">
-        <v>6462748</v>
+        <v>6462705</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,13 +7478,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7532,14 +7507,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818757</v>
+        <v>123818542</v>
       </c>
       <c r="B66" t="n">
-        <v>79406</v>
+        <v>57507</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7548,26 +7523,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7575,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572407</v>
+        <v>572542</v>
       </c>
       <c r="R66" t="n">
-        <v>6462746</v>
+        <v>6462761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7619,7 +7599,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7638,14 +7617,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123819022</v>
+        <v>123818682</v>
       </c>
       <c r="B67" t="n">
-        <v>91602</v>
+        <v>57507</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7654,26 +7633,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7681,10 +7677,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572325</v>
+        <v>572441</v>
       </c>
       <c r="R67" t="n">
-        <v>6462706</v>
+        <v>6462802</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7719,13 +7715,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818381</v>
+        <v>123818843</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572568</v>
+        <v>572420</v>
       </c>
       <c r="R9" t="n">
-        <v>6462684</v>
+        <v>6462720</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819169</v>
+        <v>123818381</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572447</v>
+        <v>572568</v>
       </c>
       <c r="R10" t="n">
-        <v>6462925</v>
+        <v>6462684</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123818843</v>
+        <v>123819169</v>
       </c>
       <c r="B11" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572420</v>
+        <v>572447</v>
       </c>
       <c r="R11" t="n">
-        <v>6462720</v>
+        <v>6462925</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819073</v>
+        <v>123819167</v>
       </c>
       <c r="B37" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4428,21 +4428,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572257</v>
+        <v>572447</v>
       </c>
       <c r="R37" t="n">
-        <v>6462806</v>
+        <v>6462925</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819179</v>
+        <v>123818936</v>
       </c>
       <c r="B38" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4530,30 +4530,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4561,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572456</v>
+        <v>572347</v>
       </c>
       <c r="R38" t="n">
-        <v>6462900</v>
+        <v>6462723</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4624,10 +4625,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819167</v>
+        <v>123819073</v>
       </c>
       <c r="B39" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4640,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4667,10 +4668,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572447</v>
+        <v>572257</v>
       </c>
       <c r="R39" t="n">
-        <v>6462925</v>
+        <v>6462806</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4730,10 +4731,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818936</v>
+        <v>123819179</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4742,31 +4743,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572347</v>
+        <v>572456</v>
       </c>
       <c r="R40" t="n">
-        <v>6462723</v>
+        <v>6462900</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818411</v>
+        <v>123819177</v>
       </c>
       <c r="B58" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,31 +6656,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6688,10 +6687,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572570</v>
+        <v>572456</v>
       </c>
       <c r="R58" t="n">
-        <v>6462742</v>
+        <v>6462900</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6751,10 +6750,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819082</v>
+        <v>123819098</v>
       </c>
       <c r="B59" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6767,21 +6766,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6794,10 +6793,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572275</v>
+        <v>572307</v>
       </c>
       <c r="R59" t="n">
-        <v>6462841</v>
+        <v>6462856</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6857,10 +6856,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819035</v>
+        <v>123818837</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>91010</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6873,21 +6872,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6900,10 +6899,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572299</v>
+        <v>572414</v>
       </c>
       <c r="R60" t="n">
-        <v>6462763</v>
+        <v>6462716</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6963,10 +6962,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123818415</v>
+        <v>123818960</v>
       </c>
       <c r="B61" t="n">
-        <v>95683</v>
+        <v>57644</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6975,31 +6974,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7007,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572570</v>
+        <v>572326</v>
       </c>
       <c r="R61" t="n">
-        <v>6462742</v>
+        <v>6462705</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7045,13 +7052,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7070,10 +7081,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123819177</v>
+        <v>123818411</v>
       </c>
       <c r="B62" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7082,30 +7093,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7113,10 +7125,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572456</v>
+        <v>572570</v>
       </c>
       <c r="R62" t="n">
-        <v>6462900</v>
+        <v>6462742</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7176,10 +7188,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819098</v>
+        <v>123819082</v>
       </c>
       <c r="B63" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7192,21 +7204,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7219,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572307</v>
+        <v>572275</v>
       </c>
       <c r="R63" t="n">
-        <v>6462856</v>
+        <v>6462841</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7282,10 +7294,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818837</v>
+        <v>123819035</v>
       </c>
       <c r="B64" t="n">
-        <v>91010</v>
+        <v>90990</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7298,21 +7310,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7325,10 +7337,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572414</v>
+        <v>572299</v>
       </c>
       <c r="R64" t="n">
-        <v>6462716</v>
+        <v>6462763</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7388,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123818960</v>
+        <v>123818415</v>
       </c>
       <c r="B65" t="n">
-        <v>57644</v>
+        <v>95683</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7400,39 +7412,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7440,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572326</v>
+        <v>572570</v>
       </c>
       <c r="R65" t="n">
-        <v>6462705</v>
+        <v>6462742</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7478,17 +7482,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819034</v>
+        <v>123818843</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572277</v>
+        <v>572420</v>
       </c>
       <c r="R2" t="n">
-        <v>6462750</v>
+        <v>6462720</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819036</v>
+        <v>123818757</v>
       </c>
       <c r="B3" t="n">
         <v>79406</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572299</v>
+        <v>572407</v>
       </c>
       <c r="R3" t="n">
-        <v>6462763</v>
+        <v>6462746</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819124</v>
+        <v>123819036</v>
       </c>
       <c r="B4" t="n">
         <v>79406</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572362</v>
+        <v>572299</v>
       </c>
       <c r="R4" t="n">
-        <v>6462874</v>
+        <v>6462763</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819088</v>
+        <v>123818873</v>
       </c>
       <c r="B5" t="n">
-        <v>78433</v>
+        <v>90974</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572276</v>
+        <v>572422</v>
       </c>
       <c r="R5" t="n">
-        <v>6462860</v>
+        <v>6462709</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818438</v>
+        <v>123819081</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>5479</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,30 +1111,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1110</v>
+        <v>101920</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572538</v>
+        <v>572275</v>
       </c>
       <c r="R6" t="n">
-        <v>6462741</v>
+        <v>6462841</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818753</v>
+        <v>123819035</v>
       </c>
       <c r="B7" t="n">
-        <v>78433</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572414</v>
+        <v>572299</v>
       </c>
       <c r="R7" t="n">
-        <v>6462768</v>
+        <v>6462763</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123818871</v>
+        <v>123819172</v>
       </c>
       <c r="B8" t="n">
-        <v>5492</v>
+        <v>90988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,32 +1325,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>1110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572422</v>
+        <v>572456</v>
       </c>
       <c r="R8" t="n">
-        <v>6462709</v>
+        <v>6462900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818843</v>
+        <v>123818643</v>
       </c>
       <c r="B9" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572420</v>
+        <v>572466</v>
       </c>
       <c r="R9" t="n">
-        <v>6462720</v>
+        <v>6462822</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818381</v>
+        <v>123818837</v>
       </c>
       <c r="B10" t="n">
         <v>91010</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572568</v>
+        <v>572414</v>
       </c>
       <c r="R10" t="n">
-        <v>6462684</v>
+        <v>6462716</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819169</v>
+        <v>123818438</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
+        <v>90988</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,25 +1643,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572447</v>
+        <v>572538</v>
       </c>
       <c r="R11" t="n">
-        <v>6462925</v>
+        <v>6462741</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819077</v>
+        <v>123818415</v>
       </c>
       <c r="B12" t="n">
-        <v>78433</v>
+        <v>95683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,30 +1749,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572247</v>
+        <v>572570</v>
       </c>
       <c r="R12" t="n">
-        <v>6462824</v>
+        <v>6462742</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819173</v>
+        <v>123818871</v>
       </c>
       <c r="B13" t="n">
-        <v>92306</v>
+        <v>5492</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,26 +1860,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1886,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572456</v>
+        <v>572422</v>
       </c>
       <c r="R13" t="n">
-        <v>6462900</v>
+        <v>6462709</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123819096</v>
+        <v>123818446</v>
       </c>
       <c r="B14" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,30 +1964,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1992,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572307</v>
+        <v>572535</v>
       </c>
       <c r="R14" t="n">
-        <v>6462856</v>
+        <v>6462771</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,7 +2059,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818646</v>
+        <v>123819074</v>
       </c>
       <c r="B15" t="n">
         <v>79406</v>
@@ -2098,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572466</v>
+        <v>572257</v>
       </c>
       <c r="R15" t="n">
-        <v>6462822</v>
+        <v>6462806</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123819022</v>
+        <v>123819157</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>78433</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2181,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572325</v>
+        <v>572446</v>
       </c>
       <c r="R16" t="n">
-        <v>6462706</v>
+        <v>6462925</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2267,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123819121</v>
+        <v>123819025</v>
       </c>
       <c r="B17" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,43 +2283,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2323,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572362</v>
+        <v>572337</v>
       </c>
       <c r="R17" t="n">
-        <v>6462874</v>
+        <v>6462716</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2361,17 +2353,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123818742</v>
+        <v>123819022</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>91602</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,31 +2390,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2434,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572433</v>
+        <v>572325</v>
       </c>
       <c r="R18" t="n">
-        <v>6462777</v>
+        <v>6462706</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2497,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123818966</v>
+        <v>123819073</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,31 +2496,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2541,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572304</v>
+        <v>572257</v>
       </c>
       <c r="R19" t="n">
-        <v>6462690</v>
+        <v>6462806</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2604,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818763</v>
+        <v>123818388</v>
       </c>
       <c r="B20" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,25 +2602,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2647,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572392</v>
+        <v>572560</v>
       </c>
       <c r="R20" t="n">
-        <v>6462722</v>
+        <v>6462694</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2710,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123818345</v>
+        <v>123819089</v>
       </c>
       <c r="B21" t="n">
-        <v>95683</v>
+        <v>79406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,31 +2708,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2754,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572575</v>
+        <v>572276</v>
       </c>
       <c r="R21" t="n">
-        <v>6462706</v>
+        <v>6462860</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2802,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819158</v>
+        <v>123818852</v>
       </c>
       <c r="B22" t="n">
         <v>79406</v>
@@ -2860,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572446</v>
+        <v>572410</v>
       </c>
       <c r="R22" t="n">
-        <v>6462925</v>
+        <v>6462725</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2923,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819149</v>
+        <v>123818331</v>
       </c>
       <c r="B23" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2939,21 +2924,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572405</v>
+        <v>572576</v>
       </c>
       <c r="R23" t="n">
-        <v>6462934</v>
+        <v>6462698</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3029,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819176</v>
+        <v>123819173</v>
       </c>
       <c r="B24" t="n">
-        <v>91010</v>
+        <v>92306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123818643</v>
+        <v>123818819</v>
       </c>
       <c r="B25" t="n">
-        <v>91010</v>
+        <v>5479</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,30 +3132,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3178,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572466</v>
+        <v>572399</v>
       </c>
       <c r="R25" t="n">
-        <v>6462822</v>
+        <v>6462693</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3241,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123818590</v>
+        <v>123818360</v>
       </c>
       <c r="B26" t="n">
         <v>79406</v>
@@ -3284,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572563</v>
+        <v>572567</v>
       </c>
       <c r="R26" t="n">
-        <v>6462748</v>
+        <v>6462723</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3347,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819032</v>
+        <v>123819167</v>
       </c>
       <c r="B27" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572284</v>
+        <v>572447</v>
       </c>
       <c r="R27" t="n">
-        <v>6462713</v>
+        <v>6462925</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3453,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818454</v>
+        <v>123819149</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,31 +3452,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3497,10 +3483,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572542</v>
+        <v>572405</v>
       </c>
       <c r="R28" t="n">
-        <v>6462761</v>
+        <v>6462934</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3560,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123819084</v>
+        <v>123818742</v>
       </c>
       <c r="B29" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3572,30 +3558,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3603,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572275</v>
+        <v>572433</v>
       </c>
       <c r="R29" t="n">
-        <v>6462841</v>
+        <v>6462777</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3666,7 +3653,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819089</v>
+        <v>123819130</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3709,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572276</v>
+        <v>572378</v>
       </c>
       <c r="R30" t="n">
-        <v>6462860</v>
+        <v>6462897</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3772,7 +3759,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818852</v>
+        <v>123819169</v>
       </c>
       <c r="B31" t="n">
         <v>79406</v>
@@ -3815,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572410</v>
+        <v>572447</v>
       </c>
       <c r="R31" t="n">
-        <v>6462725</v>
+        <v>6462925</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3878,7 +3865,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819072</v>
+        <v>123819177</v>
       </c>
       <c r="B32" t="n">
         <v>79406</v>
@@ -3921,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572298</v>
+        <v>572456</v>
       </c>
       <c r="R32" t="n">
-        <v>6462796</v>
+        <v>6462900</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3984,10 +3971,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123818873</v>
+        <v>123819098</v>
       </c>
       <c r="B33" t="n">
-        <v>90974</v>
+        <v>79406</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3996,25 +3983,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572422</v>
+        <v>572307</v>
       </c>
       <c r="R33" t="n">
-        <v>6462709</v>
+        <v>6462856</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4090,10 +4077,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819081</v>
+        <v>123819084</v>
       </c>
       <c r="B34" t="n">
-        <v>5479</v>
+        <v>79406</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,32 +4089,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4198,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123818819</v>
+        <v>123818960</v>
       </c>
       <c r="B35" t="n">
-        <v>5479</v>
+        <v>57644</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4210,32 +4195,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101920</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4243,10 +4235,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572399</v>
+        <v>572326</v>
       </c>
       <c r="R35" t="n">
-        <v>6462693</v>
+        <v>6462705</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4281,13 +4273,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4306,10 +4302,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123818938</v>
+        <v>123819124</v>
       </c>
       <c r="B36" t="n">
-        <v>74818</v>
+        <v>79406</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4318,25 +4314,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4349,10 +4345,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572347</v>
+        <v>572362</v>
       </c>
       <c r="R36" t="n">
-        <v>6462723</v>
+        <v>6462874</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4412,7 +4408,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819167</v>
+        <v>123819096</v>
       </c>
       <c r="B37" t="n">
         <v>91010</v>
@@ -4455,10 +4451,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572447</v>
+        <v>572307</v>
       </c>
       <c r="R37" t="n">
-        <v>6462925</v>
+        <v>6462856</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4518,10 +4514,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123818936</v>
+        <v>123819179</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4530,31 +4526,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4562,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572347</v>
+        <v>572456</v>
       </c>
       <c r="R38" t="n">
-        <v>6462723</v>
+        <v>6462900</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4625,10 +4620,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819073</v>
+        <v>123818411</v>
       </c>
       <c r="B39" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,30 +4632,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4668,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572257</v>
+        <v>572570</v>
       </c>
       <c r="R39" t="n">
-        <v>6462806</v>
+        <v>6462742</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4731,10 +4727,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123819179</v>
+        <v>123818646</v>
       </c>
       <c r="B40" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4747,21 +4743,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4774,10 +4770,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572456</v>
+        <v>572466</v>
       </c>
       <c r="R40" t="n">
-        <v>6462900</v>
+        <v>6462822</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4837,7 +4833,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818360</v>
+        <v>123818916</v>
       </c>
       <c r="B41" t="n">
         <v>79406</v>
@@ -4880,10 +4876,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572567</v>
+        <v>572384</v>
       </c>
       <c r="R41" t="n">
-        <v>6462723</v>
+        <v>6462675</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4943,10 +4939,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819130</v>
+        <v>123818639</v>
       </c>
       <c r="B42" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,21 +4955,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4986,10 +4982,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572378</v>
+        <v>572466</v>
       </c>
       <c r="R42" t="n">
-        <v>6462897</v>
+        <v>6462822</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5049,10 +5045,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123818629</v>
+        <v>123819077</v>
       </c>
       <c r="B43" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,31 +5057,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572515</v>
+        <v>572247</v>
       </c>
       <c r="R43" t="n">
-        <v>6462760</v>
+        <v>6462824</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5156,10 +5151,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818426</v>
+        <v>123818763</v>
       </c>
       <c r="B44" t="n">
-        <v>92271</v>
+        <v>90988</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5168,25 +5163,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1110</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5199,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572545</v>
+        <v>572392</v>
       </c>
       <c r="R44" t="n">
-        <v>6462716</v>
+        <v>6462722</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5262,10 +5257,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818826</v>
+        <v>123819121</v>
       </c>
       <c r="B45" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5274,30 +5269,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5305,10 +5313,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572399</v>
+        <v>572362</v>
       </c>
       <c r="R45" t="n">
-        <v>6462693</v>
+        <v>6462874</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5343,13 +5351,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5368,10 +5380,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123818331</v>
+        <v>123818938</v>
       </c>
       <c r="B46" t="n">
-        <v>79406</v>
+        <v>74818</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5380,25 +5392,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5411,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572576</v>
+        <v>572347</v>
       </c>
       <c r="R46" t="n">
-        <v>6462698</v>
+        <v>6462723</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5474,10 +5486,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819162</v>
+        <v>123819031</v>
       </c>
       <c r="B47" t="n">
-        <v>78433</v>
+        <v>5492</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,26 +5502,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5517,10 +5531,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572447</v>
+        <v>572284</v>
       </c>
       <c r="R47" t="n">
-        <v>6462925</v>
+        <v>6462713</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5580,10 +5594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818639</v>
+        <v>123818966</v>
       </c>
       <c r="B48" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,30 +5606,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5623,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572466</v>
+        <v>572304</v>
       </c>
       <c r="R48" t="n">
-        <v>6462822</v>
+        <v>6462690</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5686,10 +5701,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123819025</v>
+        <v>123819158</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5698,31 +5713,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5730,10 +5744,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572337</v>
+        <v>572446</v>
       </c>
       <c r="R49" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5793,10 +5807,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818446</v>
+        <v>123819082</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5805,31 +5819,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5837,10 +5850,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572535</v>
+        <v>572275</v>
       </c>
       <c r="R50" t="n">
-        <v>6462771</v>
+        <v>6462841</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5900,10 +5913,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818916</v>
+        <v>123818426</v>
       </c>
       <c r="B51" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5912,25 +5925,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5943,10 +5956,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572384</v>
+        <v>572545</v>
       </c>
       <c r="R51" t="n">
-        <v>6462675</v>
+        <v>6462716</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6006,7 +6019,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123818757</v>
+        <v>123819034</v>
       </c>
       <c r="B52" t="n">
         <v>79406</v>
@@ -6049,10 +6062,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572407</v>
+        <v>572277</v>
       </c>
       <c r="R52" t="n">
-        <v>6462746</v>
+        <v>6462750</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6112,10 +6125,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123819157</v>
+        <v>123818454</v>
       </c>
       <c r="B53" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6124,30 +6137,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6155,10 +6169,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572446</v>
+        <v>572542</v>
       </c>
       <c r="R53" t="n">
-        <v>6462925</v>
+        <v>6462761</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6218,10 +6232,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123819172</v>
+        <v>123818936</v>
       </c>
       <c r="B54" t="n">
-        <v>90988</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6230,30 +6244,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6261,10 +6276,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572456</v>
+        <v>572347</v>
       </c>
       <c r="R54" t="n">
-        <v>6462900</v>
+        <v>6462723</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6324,10 +6339,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819031</v>
+        <v>123819088</v>
       </c>
       <c r="B55" t="n">
-        <v>5492</v>
+        <v>78433</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6340,28 +6355,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6369,10 +6382,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572284</v>
+        <v>572276</v>
       </c>
       <c r="R55" t="n">
-        <v>6462713</v>
+        <v>6462860</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6432,10 +6445,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123819074</v>
+        <v>123818629</v>
       </c>
       <c r="B56" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6444,30 +6457,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6475,10 +6489,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572257</v>
+        <v>572515</v>
       </c>
       <c r="R56" t="n">
-        <v>6462806</v>
+        <v>6462760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6538,10 +6552,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818388</v>
+        <v>123818753</v>
       </c>
       <c r="B57" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6554,21 +6568,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6581,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572560</v>
+        <v>572414</v>
       </c>
       <c r="R57" t="n">
-        <v>6462694</v>
+        <v>6462768</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6644,10 +6658,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123819177</v>
+        <v>123818345</v>
       </c>
       <c r="B58" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6656,30 +6670,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6687,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572456</v>
+        <v>572575</v>
       </c>
       <c r="R58" t="n">
-        <v>6462900</v>
+        <v>6462706</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6750,10 +6765,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819098</v>
+        <v>123818381</v>
       </c>
       <c r="B59" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6766,21 +6781,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6793,10 +6808,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572307</v>
+        <v>572568</v>
       </c>
       <c r="R59" t="n">
-        <v>6462856</v>
+        <v>6462684</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6856,10 +6871,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123818837</v>
+        <v>123818826</v>
       </c>
       <c r="B60" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6872,21 +6887,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6899,10 +6914,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572414</v>
+        <v>572399</v>
       </c>
       <c r="R60" t="n">
-        <v>6462716</v>
+        <v>6462693</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6962,10 +6977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123818960</v>
+        <v>123819032</v>
       </c>
       <c r="B61" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6978,35 +6993,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7014,10 +7020,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572326</v>
+        <v>572284</v>
       </c>
       <c r="R61" t="n">
-        <v>6462705</v>
+        <v>6462713</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7052,17 +7058,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7081,10 +7083,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818411</v>
+        <v>123818590</v>
       </c>
       <c r="B62" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7093,31 +7095,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7125,10 +7126,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572570</v>
+        <v>572563</v>
       </c>
       <c r="R62" t="n">
-        <v>6462742</v>
+        <v>6462748</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7188,10 +7189,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819082</v>
+        <v>123819072</v>
       </c>
       <c r="B63" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7204,21 +7205,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7231,10 +7232,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572275</v>
+        <v>572298</v>
       </c>
       <c r="R63" t="n">
-        <v>6462841</v>
+        <v>6462796</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,10 +7295,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123819035</v>
+        <v>123819176</v>
       </c>
       <c r="B64" t="n">
-        <v>90990</v>
+        <v>91010</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7310,21 +7311,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7337,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572299</v>
+        <v>572456</v>
       </c>
       <c r="R64" t="n">
-        <v>6462763</v>
+        <v>6462900</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7400,10 +7401,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123818415</v>
+        <v>123819162</v>
       </c>
       <c r="B65" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,31 +7413,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572570</v>
+        <v>572447</v>
       </c>
       <c r="R65" t="n">
-        <v>6462742</v>
+        <v>6462925</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123818843</v>
+        <v>123819022</v>
       </c>
       <c r="B2" t="n">
-        <v>78433</v>
+        <v>91602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5454</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572420</v>
+        <v>572325</v>
       </c>
       <c r="R2" t="n">
-        <v>6462720</v>
+        <v>6462706</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123818757</v>
+        <v>123818426</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>92271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572407</v>
+        <v>572545</v>
       </c>
       <c r="R3" t="n">
-        <v>6462746</v>
+        <v>6462716</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819036</v>
+        <v>123818629</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572299</v>
+        <v>572515</v>
       </c>
       <c r="R4" t="n">
-        <v>6462763</v>
+        <v>6462760</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123818873</v>
+        <v>123818936</v>
       </c>
       <c r="B5" t="n">
-        <v>90974</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1006,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572422</v>
+        <v>572347</v>
       </c>
       <c r="R5" t="n">
-        <v>6462709</v>
+        <v>6462723</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819081</v>
+        <v>123818753</v>
       </c>
       <c r="B6" t="n">
-        <v>5479</v>
+        <v>78433</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,32 +1113,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101920</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572275</v>
+        <v>572414</v>
       </c>
       <c r="R6" t="n">
-        <v>6462841</v>
+        <v>6462768</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819035</v>
+        <v>123818916</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572299</v>
+        <v>572384</v>
       </c>
       <c r="R7" t="n">
-        <v>6462763</v>
+        <v>6462675</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819172</v>
+        <v>123819179</v>
       </c>
       <c r="B8" t="n">
-        <v>90988</v>
+        <v>78433</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1110</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818643</v>
+        <v>123818871</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>5492</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,26 +1435,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572466</v>
+        <v>572422</v>
       </c>
       <c r="R9" t="n">
-        <v>6462822</v>
+        <v>6462709</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818837</v>
+        <v>123818763</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>90988</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1110</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572414</v>
+        <v>572392</v>
       </c>
       <c r="R10" t="n">
-        <v>6462716</v>
+        <v>6462722</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818415</v>
+        <v>123818639</v>
       </c>
       <c r="B12" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,31 +1751,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1781,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572570</v>
+        <v>572466</v>
       </c>
       <c r="R12" t="n">
-        <v>6462742</v>
+        <v>6462822</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123818871</v>
+        <v>123819124</v>
       </c>
       <c r="B13" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,28 +1861,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1889,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572422</v>
+        <v>572362</v>
       </c>
       <c r="R13" t="n">
-        <v>6462709</v>
+        <v>6462874</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818446</v>
+        <v>123818852</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,31 +1963,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1996,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572535</v>
+        <v>572410</v>
       </c>
       <c r="R14" t="n">
-        <v>6462771</v>
+        <v>6462725</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123819074</v>
+        <v>123818381</v>
       </c>
       <c r="B15" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572257</v>
+        <v>572568</v>
       </c>
       <c r="R15" t="n">
-        <v>6462806</v>
+        <v>6462684</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2165,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123819157</v>
+        <v>123819173</v>
       </c>
       <c r="B16" t="n">
-        <v>78433</v>
+        <v>92306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572446</v>
+        <v>572456</v>
       </c>
       <c r="R16" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123819025</v>
+        <v>123819032</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,31 +2281,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2315,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572337</v>
+        <v>572284</v>
       </c>
       <c r="R17" t="n">
-        <v>6462716</v>
+        <v>6462713</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2378,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819022</v>
+        <v>123819176</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>91010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2391,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572325</v>
+        <v>572456</v>
       </c>
       <c r="R18" t="n">
-        <v>6462706</v>
+        <v>6462900</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2484,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819073</v>
+        <v>123819172</v>
       </c>
       <c r="B19" t="n">
-        <v>78433</v>
+        <v>90988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>1110</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572257</v>
+        <v>572456</v>
       </c>
       <c r="R19" t="n">
-        <v>6462806</v>
+        <v>6462900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2590,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818388</v>
+        <v>123819149</v>
       </c>
       <c r="B20" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,21 +2603,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572560</v>
+        <v>572405</v>
       </c>
       <c r="R20" t="n">
-        <v>6462694</v>
+        <v>6462934</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2696,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819089</v>
+        <v>123819096</v>
       </c>
       <c r="B21" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572276</v>
+        <v>572307</v>
       </c>
       <c r="R21" t="n">
-        <v>6462860</v>
+        <v>6462856</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2802,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818852</v>
+        <v>123818873</v>
       </c>
       <c r="B22" t="n">
-        <v>79406</v>
+        <v>90974</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2814,25 +2811,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4660</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2842,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572410</v>
+        <v>572422</v>
       </c>
       <c r="R22" t="n">
-        <v>6462725</v>
+        <v>6462709</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2908,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123818331</v>
+        <v>123819088</v>
       </c>
       <c r="B23" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,21 +2921,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2948,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572576</v>
+        <v>572276</v>
       </c>
       <c r="R23" t="n">
-        <v>6462698</v>
+        <v>6462860</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3014,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819173</v>
+        <v>123819162</v>
       </c>
       <c r="B24" t="n">
-        <v>92306</v>
+        <v>78433</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3027,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3057,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572456</v>
+        <v>572447</v>
       </c>
       <c r="R24" t="n">
-        <v>6462900</v>
+        <v>6462925</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3120,10 +3117,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123818819</v>
+        <v>123819073</v>
       </c>
       <c r="B25" t="n">
-        <v>5479</v>
+        <v>78433</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,32 +3129,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101920</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572399</v>
+        <v>572257</v>
       </c>
       <c r="R25" t="n">
-        <v>6462693</v>
+        <v>6462806</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3228,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123818360</v>
+        <v>123819158</v>
       </c>
       <c r="B26" t="n">
         <v>79406</v>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572567</v>
+        <v>572446</v>
       </c>
       <c r="R26" t="n">
-        <v>6462723</v>
+        <v>6462925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3334,10 +3329,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819167</v>
+        <v>123818590</v>
       </c>
       <c r="B27" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3345,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572447</v>
+        <v>572563</v>
       </c>
       <c r="R27" t="n">
-        <v>6462925</v>
+        <v>6462748</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3440,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123819149</v>
+        <v>123819169</v>
       </c>
       <c r="B28" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3483,10 +3478,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572405</v>
+        <v>572447</v>
       </c>
       <c r="R28" t="n">
-        <v>6462934</v>
+        <v>6462925</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3546,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818742</v>
+        <v>123818960</v>
       </c>
       <c r="B29" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,31 +3553,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3590,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572433</v>
+        <v>572326</v>
       </c>
       <c r="R29" t="n">
-        <v>6462777</v>
+        <v>6462705</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3628,13 +3631,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3653,7 +3660,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123819130</v>
+        <v>123818388</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3696,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572378</v>
+        <v>572560</v>
       </c>
       <c r="R30" t="n">
-        <v>6462897</v>
+        <v>6462694</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3759,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123819169</v>
+        <v>123818345</v>
       </c>
       <c r="B31" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,30 +3778,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3802,10 +3810,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572447</v>
+        <v>572575</v>
       </c>
       <c r="R31" t="n">
-        <v>6462925</v>
+        <v>6462706</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3865,7 +3873,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819177</v>
+        <v>123819036</v>
       </c>
       <c r="B32" t="n">
         <v>79406</v>
@@ -3908,10 +3916,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572456</v>
+        <v>572299</v>
       </c>
       <c r="R32" t="n">
-        <v>6462900</v>
+        <v>6462763</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3971,10 +3979,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819098</v>
+        <v>123819157</v>
       </c>
       <c r="B33" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3987,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4014,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572307</v>
+        <v>572446</v>
       </c>
       <c r="R33" t="n">
-        <v>6462856</v>
+        <v>6462925</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4077,10 +4085,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819084</v>
+        <v>123819077</v>
       </c>
       <c r="B34" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,21 +4101,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4120,10 +4128,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572275</v>
+        <v>572247</v>
       </c>
       <c r="R34" t="n">
-        <v>6462841</v>
+        <v>6462824</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4183,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123818960</v>
+        <v>123819121</v>
       </c>
       <c r="B35" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,39 +4203,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4235,10 +4247,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572326</v>
+        <v>572362</v>
       </c>
       <c r="R35" t="n">
-        <v>6462705</v>
+        <v>6462874</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4275,7 +4287,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
+          <t>Spelplats?</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4302,10 +4314,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123819124</v>
+        <v>123818966</v>
       </c>
       <c r="B36" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,30 +4326,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4345,10 +4358,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572362</v>
+        <v>572304</v>
       </c>
       <c r="R36" t="n">
-        <v>6462874</v>
+        <v>6462690</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4408,10 +4421,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819096</v>
+        <v>123819034</v>
       </c>
       <c r="B37" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,21 +4437,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4451,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572307</v>
+        <v>572277</v>
       </c>
       <c r="R37" t="n">
-        <v>6462856</v>
+        <v>6462750</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4514,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819179</v>
+        <v>123819084</v>
       </c>
       <c r="B38" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4530,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4557,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572456</v>
+        <v>572275</v>
       </c>
       <c r="R38" t="n">
-        <v>6462900</v>
+        <v>6462841</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4620,10 +4633,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123818411</v>
+        <v>123819072</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4632,31 +4645,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4664,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572570</v>
+        <v>572298</v>
       </c>
       <c r="R39" t="n">
-        <v>6462742</v>
+        <v>6462796</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4727,7 +4739,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818646</v>
+        <v>123819074</v>
       </c>
       <c r="B40" t="n">
         <v>79406</v>
@@ -4770,10 +4782,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572466</v>
+        <v>572257</v>
       </c>
       <c r="R40" t="n">
-        <v>6462822</v>
+        <v>6462806</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4833,7 +4845,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818916</v>
+        <v>123818757</v>
       </c>
       <c r="B41" t="n">
         <v>79406</v>
@@ -4876,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572384</v>
+        <v>572407</v>
       </c>
       <c r="R41" t="n">
-        <v>6462675</v>
+        <v>6462746</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4939,10 +4951,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123818639</v>
+        <v>123818938</v>
       </c>
       <c r="B42" t="n">
-        <v>78433</v>
+        <v>74818</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4951,25 +4963,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4982,10 +4994,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572466</v>
+        <v>572347</v>
       </c>
       <c r="R42" t="n">
-        <v>6462822</v>
+        <v>6462723</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5045,10 +5057,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819077</v>
+        <v>123819081</v>
       </c>
       <c r="B43" t="n">
-        <v>78433</v>
+        <v>5479</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5057,30 +5069,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>101920</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5088,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572247</v>
+        <v>572275</v>
       </c>
       <c r="R43" t="n">
-        <v>6462824</v>
+        <v>6462841</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5151,10 +5165,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818763</v>
+        <v>123818646</v>
       </c>
       <c r="B44" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5163,25 +5177,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572392</v>
+        <v>572466</v>
       </c>
       <c r="R44" t="n">
-        <v>6462722</v>
+        <v>6462822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5257,10 +5271,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123819121</v>
+        <v>123818454</v>
       </c>
       <c r="B45" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5269,43 +5283,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5313,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572362</v>
+        <v>572542</v>
       </c>
       <c r="R45" t="n">
-        <v>6462874</v>
+        <v>6462761</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5351,17 +5353,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5380,10 +5378,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123818938</v>
+        <v>123818819</v>
       </c>
       <c r="B46" t="n">
-        <v>74818</v>
+        <v>5479</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5392,30 +5390,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>101920</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572347</v>
+        <v>572399</v>
       </c>
       <c r="R46" t="n">
-        <v>6462723</v>
+        <v>6462693</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819031</v>
+        <v>123819089</v>
       </c>
       <c r="B47" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5502,28 +5502,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5531,10 +5529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572284</v>
+        <v>572276</v>
       </c>
       <c r="R47" t="n">
-        <v>6462713</v>
+        <v>6462860</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5594,7 +5592,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818966</v>
+        <v>123819025</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -5638,10 +5636,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572304</v>
+        <v>572337</v>
       </c>
       <c r="R48" t="n">
-        <v>6462690</v>
+        <v>6462716</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5701,7 +5699,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123819158</v>
+        <v>123818331</v>
       </c>
       <c r="B49" t="n">
         <v>79406</v>
@@ -5744,10 +5742,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572446</v>
+        <v>572576</v>
       </c>
       <c r="R49" t="n">
-        <v>6462925</v>
+        <v>6462698</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5913,10 +5911,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818426</v>
+        <v>123818360</v>
       </c>
       <c r="B51" t="n">
-        <v>92271</v>
+        <v>79406</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5925,25 +5923,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5956,10 +5954,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572545</v>
+        <v>572567</v>
       </c>
       <c r="R51" t="n">
-        <v>6462716</v>
+        <v>6462723</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6019,7 +6017,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123819034</v>
+        <v>123819130</v>
       </c>
       <c r="B52" t="n">
         <v>79406</v>
@@ -6062,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572277</v>
+        <v>572378</v>
       </c>
       <c r="R52" t="n">
-        <v>6462750</v>
+        <v>6462897</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6125,7 +6123,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818454</v>
+        <v>123818742</v>
       </c>
       <c r="B53" t="n">
         <v>98079</v>
@@ -6169,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572542</v>
+        <v>572433</v>
       </c>
       <c r="R53" t="n">
-        <v>6462761</v>
+        <v>6462777</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6232,7 +6230,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818936</v>
+        <v>123818446</v>
       </c>
       <c r="B54" t="n">
         <v>98079</v>
@@ -6276,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572347</v>
+        <v>572535</v>
       </c>
       <c r="R54" t="n">
-        <v>6462723</v>
+        <v>6462771</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6339,10 +6337,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819088</v>
+        <v>123819035</v>
       </c>
       <c r="B55" t="n">
-        <v>78433</v>
+        <v>90990</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6355,21 +6353,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6382,10 +6380,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572276</v>
+        <v>572299</v>
       </c>
       <c r="R55" t="n">
-        <v>6462860</v>
+        <v>6462763</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6445,10 +6443,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818629</v>
+        <v>123819167</v>
       </c>
       <c r="B56" t="n">
-        <v>95683</v>
+        <v>91010</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6457,31 +6455,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6489,10 +6486,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572515</v>
+        <v>572447</v>
       </c>
       <c r="R56" t="n">
-        <v>6462760</v>
+        <v>6462925</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6552,10 +6549,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818753</v>
+        <v>123818826</v>
       </c>
       <c r="B57" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6568,21 +6565,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6592,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572414</v>
+        <v>572399</v>
       </c>
       <c r="R57" t="n">
-        <v>6462768</v>
+        <v>6462693</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6658,10 +6655,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818345</v>
+        <v>123818843</v>
       </c>
       <c r="B58" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6670,31 +6667,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6702,10 +6698,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572575</v>
+        <v>572420</v>
       </c>
       <c r="R58" t="n">
-        <v>6462706</v>
+        <v>6462720</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6765,10 +6761,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123818381</v>
+        <v>123818415</v>
       </c>
       <c r="B59" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6777,30 +6773,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6808,10 +6805,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572568</v>
+        <v>572570</v>
       </c>
       <c r="R59" t="n">
-        <v>6462684</v>
+        <v>6462742</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6871,7 +6868,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123818826</v>
+        <v>123819177</v>
       </c>
       <c r="B60" t="n">
         <v>79406</v>
@@ -6914,10 +6911,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572399</v>
+        <v>572456</v>
       </c>
       <c r="R60" t="n">
-        <v>6462693</v>
+        <v>6462900</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6977,7 +6974,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819032</v>
+        <v>123819098</v>
       </c>
       <c r="B61" t="n">
         <v>79406</v>
@@ -7020,10 +7017,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572284</v>
+        <v>572307</v>
       </c>
       <c r="R61" t="n">
-        <v>6462713</v>
+        <v>6462856</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7083,10 +7080,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818590</v>
+        <v>123818643</v>
       </c>
       <c r="B62" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7099,21 +7096,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7126,10 +7123,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572563</v>
+        <v>572466</v>
       </c>
       <c r="R62" t="n">
-        <v>6462748</v>
+        <v>6462822</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7189,10 +7186,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819072</v>
+        <v>123819031</v>
       </c>
       <c r="B63" t="n">
-        <v>79406</v>
+        <v>5492</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7205,26 +7202,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7232,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572298</v>
+        <v>572284</v>
       </c>
       <c r="R63" t="n">
-        <v>6462796</v>
+        <v>6462713</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7295,10 +7294,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123819176</v>
+        <v>123818411</v>
       </c>
       <c r="B64" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7307,30 +7306,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572456</v>
+        <v>572570</v>
       </c>
       <c r="R64" t="n">
-        <v>6462900</v>
+        <v>6462742</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,10 +7401,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819162</v>
+        <v>123818837</v>
       </c>
       <c r="B65" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572447</v>
+        <v>572414</v>
       </c>
       <c r="R65" t="n">
-        <v>6462925</v>
+        <v>6462716</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819022</v>
+        <v>123819031</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>5492</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5454</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572325</v>
+        <v>572284</v>
       </c>
       <c r="R2" t="n">
-        <v>6462706</v>
+        <v>6462713</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123818426</v>
+        <v>123819177</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +795,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572545</v>
+        <v>572456</v>
       </c>
       <c r="R3" t="n">
-        <v>6462716</v>
+        <v>6462900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123818629</v>
+        <v>123819036</v>
       </c>
       <c r="B4" t="n">
-        <v>95683</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,31 +901,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572515</v>
+        <v>572299</v>
       </c>
       <c r="R4" t="n">
-        <v>6462760</v>
+        <v>6462763</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123818936</v>
+        <v>123819096</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,31 +1007,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572347</v>
+        <v>572307</v>
       </c>
       <c r="R5" t="n">
-        <v>6462723</v>
+        <v>6462856</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818753</v>
+        <v>123819121</v>
       </c>
       <c r="B6" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,30 +1113,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572414</v>
+        <v>572362</v>
       </c>
       <c r="R6" t="n">
-        <v>6462768</v>
+        <v>6462874</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,13 +1195,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1207,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818916</v>
+        <v>123819032</v>
       </c>
       <c r="B7" t="n">
         <v>79406</v>
@@ -1250,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572384</v>
+        <v>572284</v>
       </c>
       <c r="R7" t="n">
-        <v>6462675</v>
+        <v>6462713</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1313,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819179</v>
+        <v>123818415</v>
       </c>
       <c r="B8" t="n">
-        <v>78433</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,30 +1342,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572456</v>
+        <v>572570</v>
       </c>
       <c r="R8" t="n">
-        <v>6462900</v>
+        <v>6462742</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818871</v>
+        <v>123819022</v>
       </c>
       <c r="B9" t="n">
-        <v>5492</v>
+        <v>91602</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,28 +1453,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>5454</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572422</v>
+        <v>572325</v>
       </c>
       <c r="R9" t="n">
-        <v>6462709</v>
+        <v>6462706</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818763</v>
+        <v>123818646</v>
       </c>
       <c r="B10" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572392</v>
+        <v>572466</v>
       </c>
       <c r="R10" t="n">
-        <v>6462722</v>
+        <v>6462822</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123818438</v>
+        <v>123818446</v>
       </c>
       <c r="B11" t="n">
-        <v>90988</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,30 +1661,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1676,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572538</v>
+        <v>572535</v>
       </c>
       <c r="R11" t="n">
-        <v>6462741</v>
+        <v>6462771</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1739,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818639</v>
+        <v>123818871</v>
       </c>
       <c r="B12" t="n">
-        <v>78433</v>
+        <v>5492</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,26 +1772,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572466</v>
+        <v>572422</v>
       </c>
       <c r="R12" t="n">
-        <v>6462822</v>
+        <v>6462709</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,7 +1864,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819124</v>
+        <v>123818852</v>
       </c>
       <c r="B13" t="n">
         <v>79406</v>
@@ -1888,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572362</v>
+        <v>572410</v>
       </c>
       <c r="R13" t="n">
-        <v>6462874</v>
+        <v>6462725</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818852</v>
+        <v>123819173</v>
       </c>
       <c r="B14" t="n">
-        <v>79406</v>
+        <v>92306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572410</v>
+        <v>572456</v>
       </c>
       <c r="R14" t="n">
-        <v>6462725</v>
+        <v>6462900</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818381</v>
+        <v>123818936</v>
       </c>
       <c r="B15" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,30 +2088,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2100,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572568</v>
+        <v>572347</v>
       </c>
       <c r="R15" t="n">
-        <v>6462684</v>
+        <v>6462723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123819173</v>
+        <v>123818873</v>
       </c>
       <c r="B16" t="n">
-        <v>92306</v>
+        <v>90974</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2195,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4660</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572456</v>
+        <v>572422</v>
       </c>
       <c r="R16" t="n">
-        <v>6462900</v>
+        <v>6462709</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,7 +2289,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123819032</v>
+        <v>123819072</v>
       </c>
       <c r="B17" t="n">
         <v>79406</v>
@@ -2312,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572284</v>
+        <v>572298</v>
       </c>
       <c r="R17" t="n">
-        <v>6462713</v>
+        <v>6462796</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819176</v>
+        <v>123819124</v>
       </c>
       <c r="B18" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2411,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572456</v>
+        <v>572362</v>
       </c>
       <c r="R18" t="n">
-        <v>6462900</v>
+        <v>6462874</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2481,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819172</v>
+        <v>123818388</v>
       </c>
       <c r="B19" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2513,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572456</v>
+        <v>572560</v>
       </c>
       <c r="R19" t="n">
-        <v>6462900</v>
+        <v>6462694</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2587,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819149</v>
+        <v>123818438</v>
       </c>
       <c r="B20" t="n">
-        <v>91010</v>
+        <v>90988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,25 +2619,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>1110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572405</v>
+        <v>572538</v>
       </c>
       <c r="R20" t="n">
-        <v>6462934</v>
+        <v>6462741</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2693,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819096</v>
+        <v>123819172</v>
       </c>
       <c r="B21" t="n">
-        <v>91010</v>
+        <v>90988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,25 +2725,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>1110</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2736,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572307</v>
+        <v>572456</v>
       </c>
       <c r="R21" t="n">
-        <v>6462856</v>
+        <v>6462900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818873</v>
+        <v>123818763</v>
       </c>
       <c r="B22" t="n">
-        <v>90974</v>
+        <v>90988</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,25 +2831,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4660</v>
+        <v>1110</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2842,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572422</v>
+        <v>572392</v>
       </c>
       <c r="R22" t="n">
-        <v>6462709</v>
+        <v>6462722</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819088</v>
+        <v>123819073</v>
       </c>
       <c r="B23" t="n">
         <v>78433</v>
@@ -2948,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572276</v>
+        <v>572257</v>
       </c>
       <c r="R23" t="n">
-        <v>6462860</v>
+        <v>6462806</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3011,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819162</v>
+        <v>123819084</v>
       </c>
       <c r="B24" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3027,21 +3047,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572447</v>
+        <v>572275</v>
       </c>
       <c r="R24" t="n">
-        <v>6462925</v>
+        <v>6462841</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3117,10 +3137,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819073</v>
+        <v>123819034</v>
       </c>
       <c r="B25" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3133,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3160,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572257</v>
+        <v>572277</v>
       </c>
       <c r="R25" t="n">
-        <v>6462806</v>
+        <v>6462750</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3223,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819158</v>
+        <v>123819176</v>
       </c>
       <c r="B26" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572446</v>
+        <v>572456</v>
       </c>
       <c r="R26" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3329,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123818590</v>
+        <v>123819157</v>
       </c>
       <c r="B27" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3345,21 +3365,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572563</v>
+        <v>572446</v>
       </c>
       <c r="R27" t="n">
-        <v>6462748</v>
+        <v>6462925</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3435,10 +3455,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123819169</v>
+        <v>123818938</v>
       </c>
       <c r="B28" t="n">
-        <v>79406</v>
+        <v>74818</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,25 +3467,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3478,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572447</v>
+        <v>572347</v>
       </c>
       <c r="R28" t="n">
-        <v>6462925</v>
+        <v>6462723</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3541,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818960</v>
+        <v>123818643</v>
       </c>
       <c r="B29" t="n">
-        <v>57644</v>
+        <v>91010</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3557,35 +3577,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3593,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572326</v>
+        <v>572466</v>
       </c>
       <c r="R29" t="n">
-        <v>6462705</v>
+        <v>6462822</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3631,17 +3642,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3660,7 +3667,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123818388</v>
+        <v>123818360</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3703,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572560</v>
+        <v>572567</v>
       </c>
       <c r="R30" t="n">
-        <v>6462694</v>
+        <v>6462723</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3766,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818345</v>
+        <v>123818757</v>
       </c>
       <c r="B31" t="n">
-        <v>95683</v>
+        <v>79406</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3778,31 +3785,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3810,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572575</v>
+        <v>572407</v>
       </c>
       <c r="R31" t="n">
-        <v>6462706</v>
+        <v>6462746</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3873,10 +3879,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819036</v>
+        <v>123819149</v>
       </c>
       <c r="B32" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3889,21 +3895,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3916,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572299</v>
+        <v>572405</v>
       </c>
       <c r="R32" t="n">
-        <v>6462763</v>
+        <v>6462934</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3979,7 +3985,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819157</v>
+        <v>123819077</v>
       </c>
       <c r="B33" t="n">
         <v>78433</v>
@@ -4022,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572446</v>
+        <v>572247</v>
       </c>
       <c r="R33" t="n">
-        <v>6462925</v>
+        <v>6462824</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4085,10 +4091,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123819077</v>
+        <v>123818331</v>
       </c>
       <c r="B34" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4101,21 +4107,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4128,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572247</v>
+        <v>572576</v>
       </c>
       <c r="R34" t="n">
-        <v>6462824</v>
+        <v>6462698</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4191,10 +4197,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819121</v>
+        <v>123818629</v>
       </c>
       <c r="B35" t="n">
-        <v>56700</v>
+        <v>95683</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,39 +4213,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4247,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572362</v>
+        <v>572515</v>
       </c>
       <c r="R35" t="n">
-        <v>6462874</v>
+        <v>6462760</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4285,17 +4279,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4314,7 +4304,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123818966</v>
+        <v>123818742</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4358,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572304</v>
+        <v>572433</v>
       </c>
       <c r="R36" t="n">
-        <v>6462690</v>
+        <v>6462777</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4421,10 +4411,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819034</v>
+        <v>123818966</v>
       </c>
       <c r="B37" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4433,30 +4423,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4464,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572277</v>
+        <v>572304</v>
       </c>
       <c r="R37" t="n">
-        <v>6462750</v>
+        <v>6462690</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4527,10 +4518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819084</v>
+        <v>123818837</v>
       </c>
       <c r="B38" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,21 +4534,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4570,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572275</v>
+        <v>572414</v>
       </c>
       <c r="R38" t="n">
-        <v>6462841</v>
+        <v>6462716</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4633,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819072</v>
+        <v>123818753</v>
       </c>
       <c r="B39" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4649,21 +4640,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572298</v>
+        <v>572414</v>
       </c>
       <c r="R39" t="n">
-        <v>6462796</v>
+        <v>6462768</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4739,10 +4730,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123819074</v>
+        <v>123818411</v>
       </c>
       <c r="B40" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4751,30 +4742,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4782,10 +4774,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572257</v>
+        <v>572570</v>
       </c>
       <c r="R40" t="n">
-        <v>6462806</v>
+        <v>6462742</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4845,7 +4837,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818757</v>
+        <v>123818826</v>
       </c>
       <c r="B41" t="n">
         <v>79406</v>
@@ -4888,10 +4880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572407</v>
+        <v>572399</v>
       </c>
       <c r="R41" t="n">
-        <v>6462746</v>
+        <v>6462693</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4951,10 +4943,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123818938</v>
+        <v>123819169</v>
       </c>
       <c r="B42" t="n">
-        <v>74818</v>
+        <v>79406</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4963,25 +4955,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4994,10 +4986,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572347</v>
+        <v>572447</v>
       </c>
       <c r="R42" t="n">
-        <v>6462723</v>
+        <v>6462925</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5057,10 +5049,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819081</v>
+        <v>123819082</v>
       </c>
       <c r="B43" t="n">
-        <v>5479</v>
+        <v>78433</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5069,32 +5061,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101920</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5165,10 +5155,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818646</v>
+        <v>123819025</v>
       </c>
       <c r="B44" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5177,30 +5167,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5208,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572466</v>
+        <v>572337</v>
       </c>
       <c r="R44" t="n">
-        <v>6462822</v>
+        <v>6462716</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5271,10 +5262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818454</v>
+        <v>123819081</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>5479</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5287,27 +5278,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>101920</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5315,10 +5307,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572542</v>
+        <v>572275</v>
       </c>
       <c r="R45" t="n">
-        <v>6462761</v>
+        <v>6462841</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5378,10 +5370,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123818819</v>
+        <v>123819098</v>
       </c>
       <c r="B46" t="n">
-        <v>5479</v>
+        <v>79406</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5390,32 +5382,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5423,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572399</v>
+        <v>572307</v>
       </c>
       <c r="R46" t="n">
-        <v>6462693</v>
+        <v>6462856</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5486,10 +5476,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819089</v>
+        <v>123819162</v>
       </c>
       <c r="B47" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5502,21 +5492,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5529,10 +5519,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572276</v>
+        <v>572447</v>
       </c>
       <c r="R47" t="n">
-        <v>6462860</v>
+        <v>6462925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5592,10 +5582,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123819025</v>
+        <v>123818345</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5604,25 +5594,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5636,10 +5626,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572337</v>
+        <v>572575</v>
       </c>
       <c r="R48" t="n">
-        <v>6462716</v>
+        <v>6462706</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5699,7 +5689,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818331</v>
+        <v>123818916</v>
       </c>
       <c r="B49" t="n">
         <v>79406</v>
@@ -5742,10 +5732,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572576</v>
+        <v>572384</v>
       </c>
       <c r="R49" t="n">
-        <v>6462698</v>
+        <v>6462675</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5805,7 +5795,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123819082</v>
+        <v>123818639</v>
       </c>
       <c r="B50" t="n">
         <v>78433</v>
@@ -5848,10 +5838,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572275</v>
+        <v>572466</v>
       </c>
       <c r="R50" t="n">
-        <v>6462841</v>
+        <v>6462822</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5911,10 +5901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818360</v>
+        <v>123819179</v>
       </c>
       <c r="B51" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5927,21 +5917,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5954,10 +5944,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572567</v>
+        <v>572456</v>
       </c>
       <c r="R51" t="n">
-        <v>6462723</v>
+        <v>6462900</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6123,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818742</v>
+        <v>123818381</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6135,31 +6125,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6167,10 +6156,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572433</v>
+        <v>572568</v>
       </c>
       <c r="R53" t="n">
-        <v>6462777</v>
+        <v>6462684</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6230,10 +6219,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818446</v>
+        <v>123819089</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6242,31 +6231,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6274,10 +6262,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572535</v>
+        <v>572276</v>
       </c>
       <c r="R54" t="n">
-        <v>6462771</v>
+        <v>6462860</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6337,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819035</v>
+        <v>123819167</v>
       </c>
       <c r="B55" t="n">
-        <v>90990</v>
+        <v>91010</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6353,21 +6341,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6380,10 +6368,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572299</v>
+        <v>572447</v>
       </c>
       <c r="R55" t="n">
-        <v>6462763</v>
+        <v>6462925</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6443,10 +6431,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123819167</v>
+        <v>123818843</v>
       </c>
       <c r="B56" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6459,21 +6447,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6486,10 +6474,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572447</v>
+        <v>572420</v>
       </c>
       <c r="R56" t="n">
-        <v>6462925</v>
+        <v>6462720</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,10 +6537,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818826</v>
+        <v>123818819</v>
       </c>
       <c r="B57" t="n">
-        <v>79406</v>
+        <v>5479</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6561,30 +6549,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6655,10 +6645,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818843</v>
+        <v>123818454</v>
       </c>
       <c r="B58" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6667,30 +6657,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6698,10 +6689,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572420</v>
+        <v>572542</v>
       </c>
       <c r="R58" t="n">
-        <v>6462720</v>
+        <v>6462761</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6761,10 +6752,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123818415</v>
+        <v>123819088</v>
       </c>
       <c r="B59" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6773,31 +6764,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6805,10 +6795,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572570</v>
+        <v>572276</v>
       </c>
       <c r="R59" t="n">
-        <v>6462742</v>
+        <v>6462860</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6868,10 +6858,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819177</v>
+        <v>123819035</v>
       </c>
       <c r="B60" t="n">
-        <v>79406</v>
+        <v>90990</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6884,21 +6874,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6911,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572456</v>
+        <v>572299</v>
       </c>
       <c r="R60" t="n">
-        <v>6462900</v>
+        <v>6462763</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6974,10 +6964,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819098</v>
+        <v>123818960</v>
       </c>
       <c r="B61" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6990,26 +6980,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7017,10 +7016,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572307</v>
+        <v>572326</v>
       </c>
       <c r="R61" t="n">
-        <v>6462856</v>
+        <v>6462705</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7055,13 +7054,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7080,10 +7083,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818643</v>
+        <v>123818590</v>
       </c>
       <c r="B62" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7096,21 +7099,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7123,10 +7126,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572466</v>
+        <v>572563</v>
       </c>
       <c r="R62" t="n">
-        <v>6462822</v>
+        <v>6462748</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7186,10 +7189,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819031</v>
+        <v>123819074</v>
       </c>
       <c r="B63" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7202,28 +7205,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7231,10 +7232,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572284</v>
+        <v>572257</v>
       </c>
       <c r="R63" t="n">
-        <v>6462713</v>
+        <v>6462806</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,10 +7295,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818411</v>
+        <v>123818426</v>
       </c>
       <c r="B64" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7306,31 +7307,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572570</v>
+        <v>572545</v>
       </c>
       <c r="R64" t="n">
-        <v>6462742</v>
+        <v>6462716</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,10 +7401,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123818837</v>
+        <v>123819158</v>
       </c>
       <c r="B65" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572414</v>
+        <v>572446</v>
       </c>
       <c r="R65" t="n">
-        <v>6462716</v>
+        <v>6462925</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818542</v>
+        <v>123818682</v>
       </c>
       <c r="B66" t="n">
         <v>57507</v>
@@ -7540,9 +7540,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7555,10 +7567,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572542</v>
+        <v>572441</v>
       </c>
       <c r="R66" t="n">
-        <v>6462761</v>
+        <v>6462802</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7591,6 +7603,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7617,7 +7634,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818682</v>
+        <v>123818542</v>
       </c>
       <c r="B67" t="n">
         <v>57507</v>
@@ -7650,21 +7667,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7677,10 +7682,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572441</v>
+        <v>572542</v>
       </c>
       <c r="R67" t="n">
-        <v>6462802</v>
+        <v>6462761</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7713,11 +7718,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819121</v>
+        <v>123819032</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,43 +1113,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1157,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572362</v>
+        <v>572284</v>
       </c>
       <c r="R6" t="n">
-        <v>6462874</v>
+        <v>6462713</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,17 +1182,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819032</v>
+        <v>123818415</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,30 +1219,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572284</v>
+        <v>572570</v>
       </c>
       <c r="R7" t="n">
-        <v>6462713</v>
+        <v>6462742</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123818415</v>
+        <v>123819121</v>
       </c>
       <c r="B8" t="n">
-        <v>95683</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,27 +1330,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1374,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572570</v>
+        <v>572362</v>
       </c>
       <c r="R8" t="n">
-        <v>6462742</v>
+        <v>6462874</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,13 +1408,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818871</v>
+        <v>123818852</v>
       </c>
       <c r="B12" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,28 +1772,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1801,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572422</v>
+        <v>572410</v>
       </c>
       <c r="R12" t="n">
-        <v>6462709</v>
+        <v>6462725</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1864,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123818852</v>
+        <v>123819173</v>
       </c>
       <c r="B13" t="n">
-        <v>79406</v>
+        <v>92306</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572410</v>
+        <v>572456</v>
       </c>
       <c r="R13" t="n">
-        <v>6462725</v>
+        <v>6462900</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123819173</v>
+        <v>123818936</v>
       </c>
       <c r="B14" t="n">
-        <v>92306</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,30 +1980,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2013,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572456</v>
+        <v>572347</v>
       </c>
       <c r="R14" t="n">
-        <v>6462900</v>
+        <v>6462723</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2076,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818936</v>
+        <v>123818871</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>5492</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,31 +2087,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572347</v>
+        <v>572422</v>
       </c>
       <c r="R15" t="n">
-        <v>6462723</v>
+        <v>6462709</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -6007,10 +6007,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123819130</v>
+        <v>123818819</v>
       </c>
       <c r="B52" t="n">
-        <v>79406</v>
+        <v>5479</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6019,30 +6019,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6050,10 +6052,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572378</v>
+        <v>572399</v>
       </c>
       <c r="R52" t="n">
-        <v>6462897</v>
+        <v>6462693</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6113,7 +6115,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818381</v>
+        <v>123819167</v>
       </c>
       <c r="B53" t="n">
         <v>91010</v>
@@ -6156,10 +6158,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572568</v>
+        <v>572447</v>
       </c>
       <c r="R53" t="n">
-        <v>6462684</v>
+        <v>6462925</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6219,10 +6221,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123819089</v>
+        <v>123818843</v>
       </c>
       <c r="B54" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6235,21 +6237,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6262,10 +6264,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572276</v>
+        <v>572420</v>
       </c>
       <c r="R54" t="n">
-        <v>6462860</v>
+        <v>6462720</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6325,10 +6327,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819167</v>
+        <v>123819130</v>
       </c>
       <c r="B55" t="n">
-        <v>91010</v>
+        <v>79406</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6341,21 +6343,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6368,10 +6370,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572447</v>
+        <v>572378</v>
       </c>
       <c r="R55" t="n">
-        <v>6462925</v>
+        <v>6462897</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6431,10 +6433,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818843</v>
+        <v>123818381</v>
       </c>
       <c r="B56" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6447,21 +6449,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6474,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572420</v>
+        <v>572568</v>
       </c>
       <c r="R56" t="n">
-        <v>6462720</v>
+        <v>6462684</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6537,10 +6539,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818819</v>
+        <v>123819089</v>
       </c>
       <c r="B57" t="n">
-        <v>5479</v>
+        <v>79406</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6549,32 +6551,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572399</v>
+        <v>572276</v>
       </c>
       <c r="R57" t="n">
-        <v>6462693</v>
+        <v>6462860</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6752,10 +6752,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819088</v>
+        <v>123818590</v>
       </c>
       <c r="B59" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6768,21 +6768,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572276</v>
+        <v>572563</v>
       </c>
       <c r="R59" t="n">
-        <v>6462860</v>
+        <v>6462748</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6858,10 +6858,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819035</v>
+        <v>123819088</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>78433</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6874,21 +6874,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572299</v>
+        <v>572276</v>
       </c>
       <c r="R60" t="n">
-        <v>6462763</v>
+        <v>6462860</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6964,10 +6964,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123818960</v>
+        <v>123819035</v>
       </c>
       <c r="B61" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6980,35 +6980,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7016,10 +7007,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572326</v>
+        <v>572299</v>
       </c>
       <c r="R61" t="n">
-        <v>6462705</v>
+        <v>6462763</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7054,17 +7045,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7083,10 +7070,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818590</v>
+        <v>123818960</v>
       </c>
       <c r="B62" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7099,26 +7086,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7126,10 +7122,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572563</v>
+        <v>572326</v>
       </c>
       <c r="R62" t="n">
-        <v>6462748</v>
+        <v>6462705</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7164,13 +7160,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819031</v>
+        <v>123819034</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572284</v>
+        <v>572277</v>
       </c>
       <c r="R2" t="n">
-        <v>6462713</v>
+        <v>6462750</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -783,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819177</v>
+        <v>123818629</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572456</v>
+        <v>572515</v>
       </c>
       <c r="R3" t="n">
-        <v>6462900</v>
+        <v>6462760</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819036</v>
+        <v>123818826</v>
       </c>
       <c r="B4" t="n">
         <v>79406</v>
@@ -932,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572299</v>
+        <v>572399</v>
       </c>
       <c r="R4" t="n">
-        <v>6462763</v>
+        <v>6462693</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819096</v>
+        <v>123819077</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572307</v>
+        <v>572247</v>
       </c>
       <c r="R5" t="n">
-        <v>6462856</v>
+        <v>6462824</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819032</v>
+        <v>123819035</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572284</v>
+        <v>572299</v>
       </c>
       <c r="R6" t="n">
-        <v>6462713</v>
+        <v>6462763</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818415</v>
+        <v>123819162</v>
       </c>
       <c r="B7" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,31 +1218,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572570</v>
+        <v>572447</v>
       </c>
       <c r="R7" t="n">
-        <v>6462742</v>
+        <v>6462925</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1314,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819121</v>
+        <v>123818871</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>5492</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,42 +1324,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1370,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572362</v>
+        <v>572422</v>
       </c>
       <c r="R8" t="n">
-        <v>6462874</v>
+        <v>6462709</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1408,17 +1395,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1437,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819022</v>
+        <v>123818742</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,30 +1432,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1480,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572325</v>
+        <v>572433</v>
       </c>
       <c r="R9" t="n">
-        <v>6462706</v>
+        <v>6462777</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818646</v>
+        <v>123819073</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1543,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572466</v>
+        <v>572257</v>
       </c>
       <c r="R10" t="n">
-        <v>6462822</v>
+        <v>6462806</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123818446</v>
+        <v>123818426</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,31 +1645,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572535</v>
+        <v>572545</v>
       </c>
       <c r="R11" t="n">
-        <v>6462771</v>
+        <v>6462716</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818852</v>
+        <v>123818388</v>
       </c>
       <c r="B12" t="n">
         <v>79406</v>
@@ -1799,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572410</v>
+        <v>572560</v>
       </c>
       <c r="R12" t="n">
-        <v>6462725</v>
+        <v>6462694</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819173</v>
+        <v>123819022</v>
       </c>
       <c r="B13" t="n">
-        <v>92306</v>
+        <v>91602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>5454</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572456</v>
+        <v>572325</v>
       </c>
       <c r="R13" t="n">
-        <v>6462900</v>
+        <v>6462706</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818936</v>
+        <v>123818646</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,31 +1963,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572347</v>
+        <v>572466</v>
       </c>
       <c r="R14" t="n">
-        <v>6462723</v>
+        <v>6462822</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2075,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818871</v>
+        <v>123818643</v>
       </c>
       <c r="B15" t="n">
-        <v>5492</v>
+        <v>91010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,28 +2073,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572422</v>
+        <v>572466</v>
       </c>
       <c r="R15" t="n">
-        <v>6462709</v>
+        <v>6462822</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818873</v>
+        <v>123818916</v>
       </c>
       <c r="B16" t="n">
-        <v>90974</v>
+        <v>79406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,25 +2175,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572422</v>
+        <v>572384</v>
       </c>
       <c r="R16" t="n">
-        <v>6462709</v>
+        <v>6462675</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2289,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123819072</v>
+        <v>123818837</v>
       </c>
       <c r="B17" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,21 +2285,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2332,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572298</v>
+        <v>572414</v>
       </c>
       <c r="R17" t="n">
-        <v>6462796</v>
+        <v>6462716</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819124</v>
+        <v>123819081</v>
       </c>
       <c r="B18" t="n">
-        <v>79406</v>
+        <v>5479</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,30 +2387,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2438,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572362</v>
+        <v>572275</v>
       </c>
       <c r="R18" t="n">
-        <v>6462874</v>
+        <v>6462841</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2501,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123818388</v>
+        <v>123819173</v>
       </c>
       <c r="B19" t="n">
-        <v>79406</v>
+        <v>92306</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,21 +2499,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572560</v>
+        <v>572456</v>
       </c>
       <c r="R19" t="n">
-        <v>6462694</v>
+        <v>6462900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2607,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818438</v>
+        <v>123819084</v>
       </c>
       <c r="B20" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2619,25 +2601,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572538</v>
+        <v>572275</v>
       </c>
       <c r="R20" t="n">
-        <v>6462741</v>
+        <v>6462841</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2819,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818763</v>
+        <v>123818960</v>
       </c>
       <c r="B22" t="n">
-        <v>90988</v>
+        <v>57644</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,30 +2813,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1110</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2862,10 +2853,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572392</v>
+        <v>572326</v>
       </c>
       <c r="R22" t="n">
-        <v>6462722</v>
+        <v>6462705</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2900,13 +2891,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819073</v>
+        <v>123818360</v>
       </c>
       <c r="B23" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,21 +2936,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572257</v>
+        <v>572567</v>
       </c>
       <c r="R23" t="n">
-        <v>6462806</v>
+        <v>6462723</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3031,7 +3026,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819084</v>
+        <v>123818757</v>
       </c>
       <c r="B24" t="n">
         <v>79406</v>
@@ -3074,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572275</v>
+        <v>572407</v>
       </c>
       <c r="R24" t="n">
-        <v>6462841</v>
+        <v>6462746</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3137,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819034</v>
+        <v>123819096</v>
       </c>
       <c r="B25" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,21 +3148,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3180,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572277</v>
+        <v>572307</v>
       </c>
       <c r="R25" t="n">
-        <v>6462750</v>
+        <v>6462856</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3243,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819176</v>
+        <v>123818843</v>
       </c>
       <c r="B26" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3259,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3281,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572456</v>
+        <v>572420</v>
       </c>
       <c r="R26" t="n">
-        <v>6462900</v>
+        <v>6462720</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3349,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819157</v>
+        <v>123819074</v>
       </c>
       <c r="B27" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3392,10 +3387,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572446</v>
+        <v>572257</v>
       </c>
       <c r="R27" t="n">
-        <v>6462925</v>
+        <v>6462806</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3455,10 +3450,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818938</v>
+        <v>123819098</v>
       </c>
       <c r="B28" t="n">
-        <v>74818</v>
+        <v>79406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,25 +3462,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3498,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572347</v>
+        <v>572307</v>
       </c>
       <c r="R28" t="n">
-        <v>6462723</v>
+        <v>6462856</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,10 +3556,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818643</v>
+        <v>123818938</v>
       </c>
       <c r="B29" t="n">
-        <v>91010</v>
+        <v>74818</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3573,25 +3568,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572466</v>
+        <v>572347</v>
       </c>
       <c r="R29" t="n">
-        <v>6462822</v>
+        <v>6462723</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3667,7 +3662,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123818360</v>
+        <v>123818852</v>
       </c>
       <c r="B30" t="n">
         <v>79406</v>
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572567</v>
+        <v>572410</v>
       </c>
       <c r="R30" t="n">
-        <v>6462723</v>
+        <v>6462725</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3773,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818757</v>
+        <v>123818873</v>
       </c>
       <c r="B31" t="n">
-        <v>79406</v>
+        <v>90974</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3785,25 +3780,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4660</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3816,10 +3811,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572407</v>
+        <v>572422</v>
       </c>
       <c r="R31" t="n">
-        <v>6462746</v>
+        <v>6462709</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3879,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819149</v>
+        <v>123818345</v>
       </c>
       <c r="B32" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,30 +3886,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3922,10 +3918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572405</v>
+        <v>572575</v>
       </c>
       <c r="R32" t="n">
-        <v>6462934</v>
+        <v>6462706</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3985,10 +3981,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819077</v>
+        <v>123818381</v>
       </c>
       <c r="B33" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4001,21 +3997,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4028,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572247</v>
+        <v>572568</v>
       </c>
       <c r="R33" t="n">
-        <v>6462824</v>
+        <v>6462684</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4091,10 +4087,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123818331</v>
+        <v>123818438</v>
       </c>
       <c r="B34" t="n">
-        <v>79406</v>
+        <v>90988</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4103,25 +4099,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4130,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572576</v>
+        <v>572538</v>
       </c>
       <c r="R34" t="n">
-        <v>6462698</v>
+        <v>6462741</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4197,10 +4193,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123818629</v>
+        <v>123819121</v>
       </c>
       <c r="B35" t="n">
-        <v>95683</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4213,27 +4209,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4241,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572515</v>
+        <v>572362</v>
       </c>
       <c r="R35" t="n">
-        <v>6462760</v>
+        <v>6462874</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4279,13 +4287,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4304,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123818742</v>
+        <v>123818936</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4348,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572433</v>
+        <v>572347</v>
       </c>
       <c r="R36" t="n">
-        <v>6462777</v>
+        <v>6462723</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4411,7 +4423,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123818966</v>
+        <v>123819025</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4455,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572304</v>
+        <v>572337</v>
       </c>
       <c r="R37" t="n">
-        <v>6462690</v>
+        <v>6462716</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4518,10 +4530,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123818837</v>
+        <v>123818763</v>
       </c>
       <c r="B38" t="n">
-        <v>91010</v>
+        <v>90988</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4530,25 +4542,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>1110</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572414</v>
+        <v>572392</v>
       </c>
       <c r="R38" t="n">
-        <v>6462716</v>
+        <v>6462722</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4730,10 +4742,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818411</v>
+        <v>123819130</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4742,31 +4754,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4774,10 +4785,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572570</v>
+        <v>572378</v>
       </c>
       <c r="R40" t="n">
-        <v>6462742</v>
+        <v>6462897</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4837,7 +4848,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818826</v>
+        <v>123819124</v>
       </c>
       <c r="B41" t="n">
         <v>79406</v>
@@ -4880,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572399</v>
+        <v>572362</v>
       </c>
       <c r="R41" t="n">
-        <v>6462693</v>
+        <v>6462874</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4943,10 +4954,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819169</v>
+        <v>123819149</v>
       </c>
       <c r="B42" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,21 +4970,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4986,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572447</v>
+        <v>572405</v>
       </c>
       <c r="R42" t="n">
-        <v>6462925</v>
+        <v>6462934</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5049,10 +5060,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123819082</v>
+        <v>123818819</v>
       </c>
       <c r="B43" t="n">
-        <v>78433</v>
+        <v>5479</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,30 +5072,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>101920</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5092,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572275</v>
+        <v>572399</v>
       </c>
       <c r="R43" t="n">
-        <v>6462841</v>
+        <v>6462693</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5155,7 +5168,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123819025</v>
+        <v>123818454</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5199,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572337</v>
+        <v>572542</v>
       </c>
       <c r="R44" t="n">
-        <v>6462716</v>
+        <v>6462761</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5262,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123819081</v>
+        <v>123818966</v>
       </c>
       <c r="B45" t="n">
-        <v>5479</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5278,28 +5291,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101920</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5307,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572275</v>
+        <v>572304</v>
       </c>
       <c r="R45" t="n">
-        <v>6462841</v>
+        <v>6462690</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5370,7 +5382,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819098</v>
+        <v>123819177</v>
       </c>
       <c r="B46" t="n">
         <v>79406</v>
@@ -5413,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572307</v>
+        <v>572456</v>
       </c>
       <c r="R46" t="n">
-        <v>6462856</v>
+        <v>6462900</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5476,10 +5488,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819162</v>
+        <v>123819032</v>
       </c>
       <c r="B47" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5492,21 +5504,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5519,10 +5531,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572447</v>
+        <v>572284</v>
       </c>
       <c r="R47" t="n">
-        <v>6462925</v>
+        <v>6462713</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5582,10 +5594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818345</v>
+        <v>123819157</v>
       </c>
       <c r="B48" t="n">
-        <v>95683</v>
+        <v>78433</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5594,31 +5606,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5626,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572575</v>
+        <v>572446</v>
       </c>
       <c r="R48" t="n">
-        <v>6462706</v>
+        <v>6462925</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5689,7 +5700,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818916</v>
+        <v>123819089</v>
       </c>
       <c r="B49" t="n">
         <v>79406</v>
@@ -5732,10 +5743,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572384</v>
+        <v>572276</v>
       </c>
       <c r="R49" t="n">
-        <v>6462675</v>
+        <v>6462860</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5795,7 +5806,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818639</v>
+        <v>123819082</v>
       </c>
       <c r="B50" t="n">
         <v>78433</v>
@@ -5838,10 +5849,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572466</v>
+        <v>572275</v>
       </c>
       <c r="R50" t="n">
-        <v>6462822</v>
+        <v>6462841</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5901,10 +5912,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123819179</v>
+        <v>123819036</v>
       </c>
       <c r="B51" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5917,21 +5928,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5944,10 +5955,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572456</v>
+        <v>572299</v>
       </c>
       <c r="R51" t="n">
-        <v>6462900</v>
+        <v>6462763</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6007,10 +6018,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123818819</v>
+        <v>123818411</v>
       </c>
       <c r="B52" t="n">
-        <v>5479</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6023,28 +6034,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101920</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6052,10 +6062,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572399</v>
+        <v>572570</v>
       </c>
       <c r="R52" t="n">
-        <v>6462693</v>
+        <v>6462742</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6115,10 +6125,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123819167</v>
+        <v>123819179</v>
       </c>
       <c r="B53" t="n">
-        <v>91010</v>
+        <v>78433</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6131,21 +6141,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6158,10 +6168,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572447</v>
+        <v>572456</v>
       </c>
       <c r="R53" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6221,10 +6231,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818843</v>
+        <v>123819167</v>
       </c>
       <c r="B54" t="n">
-        <v>78433</v>
+        <v>91010</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6237,21 +6247,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6264,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572420</v>
+        <v>572447</v>
       </c>
       <c r="R54" t="n">
-        <v>6462720</v>
+        <v>6462925</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6327,10 +6337,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819130</v>
+        <v>123818415</v>
       </c>
       <c r="B55" t="n">
-        <v>79406</v>
+        <v>95683</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6339,30 +6349,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6370,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572378</v>
+        <v>572570</v>
       </c>
       <c r="R55" t="n">
-        <v>6462897</v>
+        <v>6462742</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6433,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818381</v>
+        <v>123819031</v>
       </c>
       <c r="B56" t="n">
-        <v>91010</v>
+        <v>5492</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6449,26 +6460,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6476,10 +6489,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572568</v>
+        <v>572284</v>
       </c>
       <c r="R56" t="n">
-        <v>6462684</v>
+        <v>6462713</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6539,7 +6552,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123819089</v>
+        <v>123819158</v>
       </c>
       <c r="B57" t="n">
         <v>79406</v>
@@ -6582,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572276</v>
+        <v>572446</v>
       </c>
       <c r="R57" t="n">
-        <v>6462860</v>
+        <v>6462925</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6645,10 +6658,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818454</v>
+        <v>123819072</v>
       </c>
       <c r="B58" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6657,31 +6670,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6689,10 +6701,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572542</v>
+        <v>572298</v>
       </c>
       <c r="R58" t="n">
-        <v>6462761</v>
+        <v>6462796</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6752,10 +6764,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123818590</v>
+        <v>123818639</v>
       </c>
       <c r="B59" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6768,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6795,10 +6807,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572563</v>
+        <v>572466</v>
       </c>
       <c r="R59" t="n">
-        <v>6462748</v>
+        <v>6462822</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6858,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819088</v>
+        <v>123818331</v>
       </c>
       <c r="B60" t="n">
-        <v>78433</v>
+        <v>79406</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6874,21 +6886,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6913,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572276</v>
+        <v>572576</v>
       </c>
       <c r="R60" t="n">
-        <v>6462860</v>
+        <v>6462698</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6964,10 +6976,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819035</v>
+        <v>123819169</v>
       </c>
       <c r="B61" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6980,21 +6992,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7007,10 +7019,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572299</v>
+        <v>572447</v>
       </c>
       <c r="R61" t="n">
-        <v>6462763</v>
+        <v>6462925</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7070,10 +7082,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818960</v>
+        <v>123819088</v>
       </c>
       <c r="B62" t="n">
-        <v>57644</v>
+        <v>78433</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7086,35 +7098,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7122,10 +7125,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572326</v>
+        <v>572276</v>
       </c>
       <c r="R62" t="n">
-        <v>6462705</v>
+        <v>6462860</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7160,17 +7163,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7189,10 +7188,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819074</v>
+        <v>123818446</v>
       </c>
       <c r="B63" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7201,30 +7200,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572257</v>
+        <v>572535</v>
       </c>
       <c r="R63" t="n">
-        <v>6462806</v>
+        <v>6462771</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818426</v>
+        <v>123818590</v>
       </c>
       <c r="B64" t="n">
-        <v>92271</v>
+        <v>79406</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7307,25 +7307,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572545</v>
+        <v>572563</v>
       </c>
       <c r="R64" t="n">
-        <v>6462716</v>
+        <v>6462748</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,10 +7401,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819158</v>
+        <v>123819176</v>
       </c>
       <c r="B65" t="n">
-        <v>79406</v>
+        <v>91010</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572446</v>
+        <v>572456</v>
       </c>
       <c r="R65" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818682</v>
+        <v>123818542</v>
       </c>
       <c r="B66" t="n">
         <v>57507</v>
@@ -7540,21 +7540,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7567,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572441</v>
+        <v>572542</v>
       </c>
       <c r="R66" t="n">
-        <v>6462802</v>
+        <v>6462761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7603,11 +7591,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7634,7 +7617,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818542</v>
+        <v>123818682</v>
       </c>
       <c r="B67" t="n">
         <v>57507</v>
@@ -7667,9 +7650,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7682,10 +7677,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572542</v>
+        <v>572441</v>
       </c>
       <c r="R67" t="n">
-        <v>6462761</v>
+        <v>6462802</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7718,6 +7713,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123818916</v>
+        <v>123819149</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572384</v>
+        <v>572405</v>
       </c>
       <c r="R2" t="n">
-        <v>6462675</v>
+        <v>6462934</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123818757</v>
+        <v>123819158</v>
       </c>
       <c r="B3" t="n">
         <v>79428</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572407</v>
+        <v>572446</v>
       </c>
       <c r="R3" t="n">
-        <v>6462746</v>
+        <v>6462925</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123818438</v>
+        <v>123819130</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1110</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572538</v>
+        <v>572378</v>
       </c>
       <c r="R4" t="n">
-        <v>6462741</v>
+        <v>6462897</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819073</v>
+        <v>123819089</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572257</v>
+        <v>572276</v>
       </c>
       <c r="R5" t="n">
-        <v>6462806</v>
+        <v>6462860</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123819074</v>
+        <v>123818331</v>
       </c>
       <c r="B6" t="n">
         <v>79428</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572257</v>
+        <v>572576</v>
       </c>
       <c r="R6" t="n">
-        <v>6462806</v>
+        <v>6462698</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123818446</v>
+        <v>123819169</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,31 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572535</v>
+        <v>572447</v>
       </c>
       <c r="R7" t="n">
-        <v>6462771</v>
+        <v>6462925</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819082</v>
+        <v>123819034</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572275</v>
+        <v>572277</v>
       </c>
       <c r="R8" t="n">
-        <v>6462841</v>
+        <v>6462750</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1418,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818837</v>
+        <v>123819072</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572414</v>
+        <v>572298</v>
       </c>
       <c r="R9" t="n">
-        <v>6462716</v>
+        <v>6462796</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1630,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819179</v>
+        <v>123818763</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
+        <v>91010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>1110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572456</v>
+        <v>572392</v>
       </c>
       <c r="R11" t="n">
-        <v>6462900</v>
+        <v>6462722</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1736,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818966</v>
+        <v>123819081</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>5479</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,27 +1751,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>101920</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572304</v>
+        <v>572275</v>
       </c>
       <c r="R12" t="n">
-        <v>6462690</v>
+        <v>6462841</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819025</v>
+        <v>123818438</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,31 +1855,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1887,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572337</v>
+        <v>572538</v>
       </c>
       <c r="R13" t="n">
-        <v>6462716</v>
+        <v>6462741</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1950,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123819173</v>
+        <v>123818871</v>
       </c>
       <c r="B14" t="n">
-        <v>92328</v>
+        <v>5492</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,26 +1965,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1993,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572456</v>
+        <v>572422</v>
       </c>
       <c r="R14" t="n">
-        <v>6462900</v>
+        <v>6462709</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2056,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818331</v>
+        <v>123818629</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,30 +2069,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2099,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572576</v>
+        <v>572515</v>
       </c>
       <c r="R15" t="n">
-        <v>6462698</v>
+        <v>6462760</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2162,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818388</v>
+        <v>123818753</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572560</v>
+        <v>572414</v>
       </c>
       <c r="R16" t="n">
-        <v>6462694</v>
+        <v>6462768</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2268,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123818629</v>
+        <v>123819077</v>
       </c>
       <c r="B17" t="n">
-        <v>95705</v>
+        <v>78455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,31 +2282,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572515</v>
+        <v>572247</v>
       </c>
       <c r="R17" t="n">
-        <v>6462760</v>
+        <v>6462824</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123818360</v>
+        <v>123819173</v>
       </c>
       <c r="B18" t="n">
-        <v>79428</v>
+        <v>92328</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572567</v>
+        <v>572456</v>
       </c>
       <c r="R18" t="n">
-        <v>6462723</v>
+        <v>6462900</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2481,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123818646</v>
+        <v>123819121</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,30 +2494,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2524,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572466</v>
+        <v>572362</v>
       </c>
       <c r="R19" t="n">
-        <v>6462822</v>
+        <v>6462874</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2562,13 +2576,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,7 +2605,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819098</v>
+        <v>123818360</v>
       </c>
       <c r="B20" t="n">
         <v>79428</v>
@@ -2630,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572307</v>
+        <v>572567</v>
       </c>
       <c r="R20" t="n">
-        <v>6462856</v>
+        <v>6462723</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2693,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819072</v>
+        <v>123819035</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2727,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2736,10 +2754,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572298</v>
+        <v>572299</v>
       </c>
       <c r="R21" t="n">
-        <v>6462796</v>
+        <v>6462763</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2799,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819176</v>
+        <v>123818415</v>
       </c>
       <c r="B22" t="n">
-        <v>91032</v>
+        <v>95705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,30 +2829,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2842,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572456</v>
+        <v>572570</v>
       </c>
       <c r="R22" t="n">
-        <v>6462900</v>
+        <v>6462742</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819121</v>
+        <v>123819177</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,43 +2936,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2961,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572362</v>
+        <v>572456</v>
       </c>
       <c r="R23" t="n">
-        <v>6462874</v>
+        <v>6462900</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2999,17 +3005,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3028,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123818643</v>
+        <v>123819084</v>
       </c>
       <c r="B24" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572466</v>
+        <v>572275</v>
       </c>
       <c r="R24" t="n">
-        <v>6462822</v>
+        <v>6462841</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3134,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123818873</v>
+        <v>123818852</v>
       </c>
       <c r="B25" t="n">
-        <v>90996</v>
+        <v>79428</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3146,25 +3148,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572422</v>
+        <v>572410</v>
       </c>
       <c r="R25" t="n">
-        <v>6462709</v>
+        <v>6462725</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3240,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819177</v>
+        <v>123819157</v>
       </c>
       <c r="B26" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,21 +3258,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572456</v>
+        <v>572446</v>
       </c>
       <c r="R26" t="n">
-        <v>6462900</v>
+        <v>6462925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3346,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819169</v>
+        <v>123819176</v>
       </c>
       <c r="B27" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3362,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572447</v>
+        <v>572456</v>
       </c>
       <c r="R27" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3452,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818345</v>
+        <v>123818381</v>
       </c>
       <c r="B28" t="n">
-        <v>95705</v>
+        <v>91032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3464,31 +3466,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3496,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572575</v>
+        <v>572568</v>
       </c>
       <c r="R28" t="n">
-        <v>6462706</v>
+        <v>6462684</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3559,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123819096</v>
+        <v>123819036</v>
       </c>
       <c r="B29" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,21 +3576,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572307</v>
+        <v>572299</v>
       </c>
       <c r="R29" t="n">
-        <v>6462856</v>
+        <v>6462763</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3665,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123818938</v>
+        <v>123818757</v>
       </c>
       <c r="B30" t="n">
-        <v>74840</v>
+        <v>79428</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,25 +3678,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572347</v>
+        <v>572407</v>
       </c>
       <c r="R30" t="n">
-        <v>6462723</v>
+        <v>6462746</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3771,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818763</v>
+        <v>123818819</v>
       </c>
       <c r="B31" t="n">
-        <v>91010</v>
+        <v>5479</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,30 +3784,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1110</v>
+        <v>101920</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3814,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572392</v>
+        <v>572399</v>
       </c>
       <c r="R31" t="n">
-        <v>6462722</v>
+        <v>6462693</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3877,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123818843</v>
+        <v>123818742</v>
       </c>
       <c r="B32" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3889,30 +3892,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3920,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572420</v>
+        <v>572433</v>
       </c>
       <c r="R32" t="n">
-        <v>6462720</v>
+        <v>6462777</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3983,10 +3987,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819088</v>
+        <v>123818873</v>
       </c>
       <c r="B33" t="n">
-        <v>78455</v>
+        <v>90996</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3995,25 +3999,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4660</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4026,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572276</v>
+        <v>572422</v>
       </c>
       <c r="R33" t="n">
-        <v>6462860</v>
+        <v>6462709</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4089,10 +4093,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123818819</v>
+        <v>123818388</v>
       </c>
       <c r="B34" t="n">
-        <v>5479</v>
+        <v>79428</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4101,32 +4105,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4134,10 +4136,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572399</v>
+        <v>572560</v>
       </c>
       <c r="R34" t="n">
-        <v>6462693</v>
+        <v>6462694</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4197,10 +4199,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819167</v>
+        <v>123818966</v>
       </c>
       <c r="B35" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4209,30 +4211,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4240,10 +4243,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572447</v>
+        <v>572304</v>
       </c>
       <c r="R35" t="n">
-        <v>6462925</v>
+        <v>6462690</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4303,10 +4306,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123819035</v>
+        <v>123819088</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>78455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,21 +4322,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4346,10 +4349,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572299</v>
+        <v>572276</v>
       </c>
       <c r="R36" t="n">
-        <v>6462763</v>
+        <v>6462860</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4409,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819034</v>
+        <v>123819167</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,21 +4428,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572277</v>
+        <v>572447</v>
       </c>
       <c r="R37" t="n">
-        <v>6462750</v>
+        <v>6462925</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4515,7 +4518,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819130</v>
+        <v>123819074</v>
       </c>
       <c r="B38" t="n">
         <v>79428</v>
@@ -4558,10 +4561,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572378</v>
+        <v>572257</v>
       </c>
       <c r="R38" t="n">
-        <v>6462897</v>
+        <v>6462806</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4621,7 +4624,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123818852</v>
+        <v>123819124</v>
       </c>
       <c r="B39" t="n">
         <v>79428</v>
@@ -4664,10 +4667,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572410</v>
+        <v>572362</v>
       </c>
       <c r="R39" t="n">
-        <v>6462725</v>
+        <v>6462874</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4727,10 +4730,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818960</v>
+        <v>123818826</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4743,35 +4746,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4779,10 +4773,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572326</v>
+        <v>572399</v>
       </c>
       <c r="R40" t="n">
-        <v>6462705</v>
+        <v>6462693</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4817,17 +4811,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4846,10 +4836,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818742</v>
+        <v>123818426</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4858,31 +4848,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4890,10 +4879,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572433</v>
+        <v>572545</v>
       </c>
       <c r="R41" t="n">
-        <v>6462777</v>
+        <v>6462716</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4953,10 +4942,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819172</v>
+        <v>123819073</v>
       </c>
       <c r="B42" t="n">
-        <v>91010</v>
+        <v>78455</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4965,25 +4954,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1110</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4996,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572456</v>
+        <v>572257</v>
       </c>
       <c r="R42" t="n">
-        <v>6462900</v>
+        <v>6462806</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5059,10 +5048,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123818454</v>
+        <v>123818590</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5071,31 +5060,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5103,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572542</v>
+        <v>572563</v>
       </c>
       <c r="R43" t="n">
-        <v>6462761</v>
+        <v>6462748</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5166,10 +5154,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123818936</v>
+        <v>123819031</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>5492</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5178,31 +5166,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5210,10 +5199,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572347</v>
+        <v>572284</v>
       </c>
       <c r="R44" t="n">
-        <v>6462723</v>
+        <v>6462713</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5380,10 +5369,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819031</v>
+        <v>123818446</v>
       </c>
       <c r="B46" t="n">
-        <v>5492</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5392,32 +5381,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5425,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572284</v>
+        <v>572535</v>
       </c>
       <c r="R46" t="n">
-        <v>6462713</v>
+        <v>6462771</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5488,10 +5476,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123819162</v>
+        <v>123818960</v>
       </c>
       <c r="B47" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5504,26 +5492,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5531,10 +5528,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572447</v>
+        <v>572326</v>
       </c>
       <c r="R47" t="n">
-        <v>6462925</v>
+        <v>6462705</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5569,13 +5566,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5594,10 +5595,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123819149</v>
+        <v>123818916</v>
       </c>
       <c r="B48" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5610,21 +5611,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5637,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572405</v>
+        <v>572384</v>
       </c>
       <c r="R48" t="n">
-        <v>6462934</v>
+        <v>6462675</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5700,7 +5701,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123818753</v>
+        <v>123819162</v>
       </c>
       <c r="B49" t="n">
         <v>78455</v>
@@ -5743,10 +5744,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572414</v>
+        <v>572447</v>
       </c>
       <c r="R49" t="n">
-        <v>6462768</v>
+        <v>6462925</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5806,10 +5807,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123819077</v>
+        <v>123819098</v>
       </c>
       <c r="B50" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5822,21 +5823,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5849,10 +5850,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572247</v>
+        <v>572307</v>
       </c>
       <c r="R50" t="n">
-        <v>6462824</v>
+        <v>6462856</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5912,10 +5913,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123819084</v>
+        <v>123818936</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5924,30 +5925,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5955,10 +5957,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572275</v>
+        <v>572347</v>
       </c>
       <c r="R51" t="n">
-        <v>6462841</v>
+        <v>6462723</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6018,7 +6020,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123818826</v>
+        <v>123818646</v>
       </c>
       <c r="B52" t="n">
         <v>79428</v>
@@ -6061,10 +6063,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572399</v>
+        <v>572466</v>
       </c>
       <c r="R52" t="n">
-        <v>6462693</v>
+        <v>6462822</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6124,10 +6126,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818415</v>
+        <v>123819082</v>
       </c>
       <c r="B53" t="n">
-        <v>95705</v>
+        <v>78455</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6136,31 +6138,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6168,10 +6169,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572570</v>
+        <v>572275</v>
       </c>
       <c r="R53" t="n">
-        <v>6462742</v>
+        <v>6462841</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6231,10 +6232,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123819158</v>
+        <v>123818643</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6247,21 +6248,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6275,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572446</v>
+        <v>572466</v>
       </c>
       <c r="R54" t="n">
-        <v>6462925</v>
+        <v>6462822</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6337,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819089</v>
+        <v>123819172</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>91010</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6349,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>1110</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6380,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572276</v>
+        <v>572456</v>
       </c>
       <c r="R55" t="n">
-        <v>6462860</v>
+        <v>6462900</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6443,10 +6444,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123818871</v>
+        <v>123819179</v>
       </c>
       <c r="B56" t="n">
-        <v>5492</v>
+        <v>78455</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6459,28 +6460,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6488,10 +6487,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572422</v>
+        <v>572456</v>
       </c>
       <c r="R56" t="n">
-        <v>6462709</v>
+        <v>6462900</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6551,10 +6550,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818426</v>
+        <v>123818938</v>
       </c>
       <c r="B57" t="n">
-        <v>92293</v>
+        <v>74840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6567,21 +6566,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6594,10 +6593,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572545</v>
+        <v>572347</v>
       </c>
       <c r="R57" t="n">
-        <v>6462716</v>
+        <v>6462723</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6657,10 +6656,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123819081</v>
+        <v>123819022</v>
       </c>
       <c r="B58" t="n">
-        <v>5479</v>
+        <v>91624</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6669,32 +6668,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>101920</v>
+        <v>5454</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6702,10 +6699,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572275</v>
+        <v>572325</v>
       </c>
       <c r="R58" t="n">
-        <v>6462841</v>
+        <v>6462706</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6765,10 +6762,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819022</v>
+        <v>123819025</v>
       </c>
       <c r="B59" t="n">
-        <v>91624</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6777,30 +6774,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6808,10 +6806,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572325</v>
+        <v>572337</v>
       </c>
       <c r="R59" t="n">
-        <v>6462706</v>
+        <v>6462716</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6871,10 +6869,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123819124</v>
+        <v>123818345</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>95705</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6883,30 +6881,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6914,10 +6913,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572362</v>
+        <v>572575</v>
       </c>
       <c r="R60" t="n">
-        <v>6462874</v>
+        <v>6462706</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6977,10 +6976,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819036</v>
+        <v>123819096</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6993,21 +6992,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7020,10 +7019,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572299</v>
+        <v>572307</v>
       </c>
       <c r="R61" t="n">
-        <v>6462763</v>
+        <v>6462856</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7083,7 +7082,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123819157</v>
+        <v>123818843</v>
       </c>
       <c r="B62" t="n">
         <v>78455</v>
@@ -7126,10 +7125,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572446</v>
+        <v>572420</v>
       </c>
       <c r="R62" t="n">
-        <v>6462925</v>
+        <v>6462720</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7189,7 +7188,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123818381</v>
+        <v>123818837</v>
       </c>
       <c r="B63" t="n">
         <v>91032</v>
@@ -7232,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572568</v>
+        <v>572414</v>
       </c>
       <c r="R63" t="n">
-        <v>6462684</v>
+        <v>6462716</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7295,7 +7294,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818590</v>
+        <v>123819032</v>
       </c>
       <c r="B64" t="n">
         <v>79428</v>
@@ -7338,10 +7337,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572563</v>
+        <v>572284</v>
       </c>
       <c r="R64" t="n">
-        <v>6462748</v>
+        <v>6462713</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,10 +7400,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819032</v>
+        <v>123818454</v>
       </c>
       <c r="B65" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7413,30 +7412,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572284</v>
+        <v>572542</v>
       </c>
       <c r="R65" t="n">
-        <v>6462713</v>
+        <v>6462761</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818682</v>
+        <v>123818542</v>
       </c>
       <c r="B66" t="n">
         <v>57529</v>
@@ -7540,21 +7540,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7567,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572441</v>
+        <v>572542</v>
       </c>
       <c r="R66" t="n">
-        <v>6462802</v>
+        <v>6462761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7603,11 +7591,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7634,7 +7617,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818542</v>
+        <v>123818682</v>
       </c>
       <c r="B67" t="n">
         <v>57529</v>
@@ -7667,9 +7650,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7682,10 +7677,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572542</v>
+        <v>572441</v>
       </c>
       <c r="R67" t="n">
-        <v>6462761</v>
+        <v>6462802</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7718,6 +7713,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123819149</v>
+        <v>123818757</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572405</v>
+        <v>572407</v>
       </c>
       <c r="R2" t="n">
-        <v>6462934</v>
+        <v>6462746</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819158</v>
+        <v>123819022</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>91624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572446</v>
+        <v>572325</v>
       </c>
       <c r="R3" t="n">
-        <v>6462925</v>
+        <v>6462706</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819130</v>
+        <v>123819025</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572378</v>
+        <v>572337</v>
       </c>
       <c r="R4" t="n">
-        <v>6462897</v>
+        <v>6462716</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819089</v>
+        <v>123819173</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>92328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572276</v>
+        <v>572456</v>
       </c>
       <c r="R5" t="n">
-        <v>6462860</v>
+        <v>6462900</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818331</v>
+        <v>123818852</v>
       </c>
       <c r="B6" t="n">
         <v>79428</v>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572576</v>
+        <v>572410</v>
       </c>
       <c r="R6" t="n">
-        <v>6462698</v>
+        <v>6462725</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819169</v>
+        <v>123819121</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,30 +1218,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572447</v>
+        <v>572362</v>
       </c>
       <c r="R7" t="n">
-        <v>6462925</v>
+        <v>6462874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,13 +1300,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1311,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819034</v>
+        <v>123819035</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572277</v>
+        <v>572299</v>
       </c>
       <c r="R8" t="n">
-        <v>6462750</v>
+        <v>6462763</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123819072</v>
+        <v>123818966</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,30 +1447,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572298</v>
+        <v>572304</v>
       </c>
       <c r="R9" t="n">
-        <v>6462796</v>
+        <v>6462690</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123818639</v>
+        <v>123819032</v>
       </c>
       <c r="B10" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1558,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572466</v>
+        <v>572284</v>
       </c>
       <c r="R10" t="n">
-        <v>6462822</v>
+        <v>6462713</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123818763</v>
+        <v>123819162</v>
       </c>
       <c r="B11" t="n">
-        <v>91010</v>
+        <v>78455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1660,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572392</v>
+        <v>572447</v>
       </c>
       <c r="R11" t="n">
-        <v>6462722</v>
+        <v>6462925</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1735,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123819081</v>
+        <v>123818753</v>
       </c>
       <c r="B12" t="n">
-        <v>5479</v>
+        <v>78455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,32 +1766,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101920</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1780,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572275</v>
+        <v>572414</v>
       </c>
       <c r="R12" t="n">
-        <v>6462841</v>
+        <v>6462768</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123818438</v>
+        <v>123819172</v>
       </c>
       <c r="B13" t="n">
         <v>91010</v>
@@ -1886,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572538</v>
+        <v>572456</v>
       </c>
       <c r="R13" t="n">
-        <v>6462741</v>
+        <v>6462900</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,10 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818871</v>
+        <v>123818415</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>95705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,32 +1978,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1994,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572422</v>
+        <v>572570</v>
       </c>
       <c r="R14" t="n">
-        <v>6462709</v>
+        <v>6462742</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818629</v>
+        <v>123818936</v>
       </c>
       <c r="B15" t="n">
-        <v>95705</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572515</v>
+        <v>572347</v>
       </c>
       <c r="R15" t="n">
-        <v>6462760</v>
+        <v>6462723</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818753</v>
+        <v>123818360</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2196,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572414</v>
+        <v>572567</v>
       </c>
       <c r="R16" t="n">
-        <v>6462768</v>
+        <v>6462723</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2270,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123819077</v>
+        <v>123818590</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2302,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572247</v>
+        <v>572563</v>
       </c>
       <c r="R17" t="n">
-        <v>6462824</v>
+        <v>6462748</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2376,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819173</v>
+        <v>123819072</v>
       </c>
       <c r="B18" t="n">
-        <v>92328</v>
+        <v>79428</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572456</v>
+        <v>572298</v>
       </c>
       <c r="R18" t="n">
-        <v>6462900</v>
+        <v>6462796</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2482,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819121</v>
+        <v>123819088</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>78455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,43 +2510,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2538,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572362</v>
+        <v>572276</v>
       </c>
       <c r="R19" t="n">
-        <v>6462874</v>
+        <v>6462860</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2576,17 +2579,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2605,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818360</v>
+        <v>123818742</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,30 +2616,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572567</v>
+        <v>572433</v>
       </c>
       <c r="R20" t="n">
-        <v>6462723</v>
+        <v>6462777</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819035</v>
+        <v>123818629</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>95705</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,30 +2723,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2754,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572299</v>
+        <v>572515</v>
       </c>
       <c r="R21" t="n">
-        <v>6462763</v>
+        <v>6462760</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818415</v>
+        <v>123818873</v>
       </c>
       <c r="B22" t="n">
-        <v>95705</v>
+        <v>90996</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2833,27 +2834,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>4660</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572570</v>
+        <v>572422</v>
       </c>
       <c r="R22" t="n">
-        <v>6462742</v>
+        <v>6462709</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819177</v>
+        <v>123819073</v>
       </c>
       <c r="B23" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572456</v>
+        <v>572257</v>
       </c>
       <c r="R23" t="n">
-        <v>6462900</v>
+        <v>6462806</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819084</v>
+        <v>123819157</v>
       </c>
       <c r="B24" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572275</v>
+        <v>572446</v>
       </c>
       <c r="R24" t="n">
-        <v>6462841</v>
+        <v>6462925</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123818852</v>
+        <v>123819176</v>
       </c>
       <c r="B25" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572410</v>
+        <v>572456</v>
       </c>
       <c r="R25" t="n">
-        <v>6462725</v>
+        <v>6462900</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819157</v>
+        <v>123819077</v>
       </c>
       <c r="B26" t="n">
         <v>78455</v>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572446</v>
+        <v>572247</v>
       </c>
       <c r="R26" t="n">
-        <v>6462925</v>
+        <v>6462824</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819176</v>
+        <v>123819082</v>
       </c>
       <c r="B27" t="n">
-        <v>91032</v>
+        <v>78455</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,21 +3364,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572456</v>
+        <v>572275</v>
       </c>
       <c r="R27" t="n">
-        <v>6462900</v>
+        <v>6462841</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123818381</v>
+        <v>123819167</v>
       </c>
       <c r="B28" t="n">
         <v>91032</v>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572568</v>
+        <v>572447</v>
       </c>
       <c r="R28" t="n">
-        <v>6462684</v>
+        <v>6462925</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3560,10 +3560,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123819036</v>
+        <v>123818837</v>
       </c>
       <c r="B29" t="n">
-        <v>79428</v>
+        <v>91032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3576,21 +3576,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572299</v>
+        <v>572414</v>
       </c>
       <c r="R29" t="n">
-        <v>6462763</v>
+        <v>6462716</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123818757</v>
+        <v>123818960</v>
       </c>
       <c r="B30" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,26 +3682,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3709,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572407</v>
+        <v>572326</v>
       </c>
       <c r="R30" t="n">
-        <v>6462746</v>
+        <v>6462705</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3747,13 +3756,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3772,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818819</v>
+        <v>123818388</v>
       </c>
       <c r="B31" t="n">
-        <v>5479</v>
+        <v>79428</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,32 +3797,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101920</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3817,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572399</v>
+        <v>572560</v>
       </c>
       <c r="R31" t="n">
-        <v>6462693</v>
+        <v>6462694</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3880,10 +3891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123818742</v>
+        <v>123819089</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3892,31 +3903,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572433</v>
+        <v>572276</v>
       </c>
       <c r="R32" t="n">
-        <v>6462777</v>
+        <v>6462860</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3987,10 +3997,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123818873</v>
+        <v>123819036</v>
       </c>
       <c r="B33" t="n">
-        <v>90996</v>
+        <v>79428</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3999,25 +4009,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4660</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4030,10 +4040,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572422</v>
+        <v>572299</v>
       </c>
       <c r="R33" t="n">
-        <v>6462709</v>
+        <v>6462763</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4093,7 +4103,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123818388</v>
+        <v>123818331</v>
       </c>
       <c r="B34" t="n">
         <v>79428</v>
@@ -4136,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572560</v>
+        <v>572576</v>
       </c>
       <c r="R34" t="n">
-        <v>6462694</v>
+        <v>6462698</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4199,10 +4209,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123818966</v>
+        <v>123819169</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4211,31 +4221,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4243,10 +4252,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572304</v>
+        <v>572447</v>
       </c>
       <c r="R35" t="n">
-        <v>6462690</v>
+        <v>6462925</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4306,10 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123819088</v>
+        <v>123819149</v>
       </c>
       <c r="B36" t="n">
-        <v>78455</v>
+        <v>91032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,21 +4331,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4349,10 +4358,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572276</v>
+        <v>572405</v>
       </c>
       <c r="R36" t="n">
-        <v>6462860</v>
+        <v>6462934</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4412,10 +4421,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123819167</v>
+        <v>123818446</v>
       </c>
       <c r="B37" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,30 +4433,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4455,10 +4465,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572447</v>
+        <v>572535</v>
       </c>
       <c r="R37" t="n">
-        <v>6462925</v>
+        <v>6462771</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4518,7 +4528,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819074</v>
+        <v>123819158</v>
       </c>
       <c r="B38" t="n">
         <v>79428</v>
@@ -4561,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572257</v>
+        <v>572446</v>
       </c>
       <c r="R38" t="n">
-        <v>6462806</v>
+        <v>6462925</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4624,7 +4634,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819124</v>
+        <v>123819034</v>
       </c>
       <c r="B39" t="n">
         <v>79428</v>
@@ -4667,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572362</v>
+        <v>572277</v>
       </c>
       <c r="R39" t="n">
-        <v>6462874</v>
+        <v>6462750</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4730,7 +4740,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123818826</v>
+        <v>123819074</v>
       </c>
       <c r="B40" t="n">
         <v>79428</v>
@@ -4773,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572399</v>
+        <v>572257</v>
       </c>
       <c r="R40" t="n">
-        <v>6462693</v>
+        <v>6462806</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4836,10 +4846,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818426</v>
+        <v>123818938</v>
       </c>
       <c r="B41" t="n">
-        <v>92293</v>
+        <v>74840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,21 +4862,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4879,10 +4889,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572545</v>
+        <v>572347</v>
       </c>
       <c r="R41" t="n">
-        <v>6462716</v>
+        <v>6462723</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4942,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123819073</v>
+        <v>123818345</v>
       </c>
       <c r="B42" t="n">
-        <v>78455</v>
+        <v>95705</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,30 +4964,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4985,10 +4996,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572257</v>
+        <v>572575</v>
       </c>
       <c r="R42" t="n">
-        <v>6462806</v>
+        <v>6462706</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5048,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123818590</v>
+        <v>123818411</v>
       </c>
       <c r="B43" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5060,30 +5071,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5091,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572563</v>
+        <v>572570</v>
       </c>
       <c r="R43" t="n">
-        <v>6462748</v>
+        <v>6462742</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5154,10 +5166,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123819031</v>
+        <v>123819177</v>
       </c>
       <c r="B44" t="n">
-        <v>5492</v>
+        <v>79428</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5170,28 +5182,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5199,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572284</v>
+        <v>572456</v>
       </c>
       <c r="R44" t="n">
-        <v>6462713</v>
+        <v>6462900</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5262,10 +5272,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818411</v>
+        <v>123818643</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5274,31 +5284,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5306,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572570</v>
+        <v>572466</v>
       </c>
       <c r="R45" t="n">
-        <v>6462742</v>
+        <v>6462822</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5369,10 +5378,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123818446</v>
+        <v>123819096</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5381,31 +5390,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5413,10 +5421,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572535</v>
+        <v>572307</v>
       </c>
       <c r="R46" t="n">
-        <v>6462771</v>
+        <v>6462856</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5476,10 +5484,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123818960</v>
+        <v>123818871</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>5492</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5492,35 +5500,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>101410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5528,10 +5529,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572326</v>
+        <v>572422</v>
       </c>
       <c r="R47" t="n">
-        <v>6462705</v>
+        <v>6462709</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5566,17 +5567,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5595,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123818916</v>
+        <v>123819031</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>5492</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5611,26 +5608,28 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5638,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572384</v>
+        <v>572284</v>
       </c>
       <c r="R48" t="n">
-        <v>6462675</v>
+        <v>6462713</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5701,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123819162</v>
+        <v>123819130</v>
       </c>
       <c r="B49" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5717,21 +5716,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5744,10 +5743,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572447</v>
+        <v>572378</v>
       </c>
       <c r="R49" t="n">
-        <v>6462925</v>
+        <v>6462897</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5807,10 +5806,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123819098</v>
+        <v>123818639</v>
       </c>
       <c r="B50" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5823,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5850,10 +5849,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572307</v>
+        <v>572466</v>
       </c>
       <c r="R50" t="n">
-        <v>6462856</v>
+        <v>6462822</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5913,10 +5912,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818936</v>
+        <v>123818381</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5925,31 +5924,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5957,10 +5955,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572347</v>
+        <v>572568</v>
       </c>
       <c r="R51" t="n">
-        <v>6462723</v>
+        <v>6462684</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6020,7 +6018,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123818646</v>
+        <v>123819098</v>
       </c>
       <c r="B52" t="n">
         <v>79428</v>
@@ -6063,10 +6061,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572466</v>
+        <v>572307</v>
       </c>
       <c r="R52" t="n">
-        <v>6462822</v>
+        <v>6462856</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6126,10 +6124,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123819082</v>
+        <v>123818454</v>
       </c>
       <c r="B53" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6138,30 +6136,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6169,10 +6168,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572275</v>
+        <v>572542</v>
       </c>
       <c r="R53" t="n">
-        <v>6462841</v>
+        <v>6462761</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6232,10 +6231,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818643</v>
+        <v>123818826</v>
       </c>
       <c r="B54" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6248,21 +6247,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6275,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572466</v>
+        <v>572399</v>
       </c>
       <c r="R54" t="n">
-        <v>6462822</v>
+        <v>6462693</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6338,10 +6337,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123819172</v>
+        <v>123818426</v>
       </c>
       <c r="B55" t="n">
-        <v>91010</v>
+        <v>92293</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6350,25 +6349,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1110</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6380,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572456</v>
+        <v>572545</v>
       </c>
       <c r="R55" t="n">
-        <v>6462900</v>
+        <v>6462716</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6444,10 +6443,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123819179</v>
+        <v>123819081</v>
       </c>
       <c r="B56" t="n">
-        <v>78455</v>
+        <v>5479</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6456,30 +6455,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>101920</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6487,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572456</v>
+        <v>572275</v>
       </c>
       <c r="R56" t="n">
-        <v>6462900</v>
+        <v>6462841</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6550,10 +6551,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818938</v>
+        <v>123818438</v>
       </c>
       <c r="B57" t="n">
-        <v>74840</v>
+        <v>91010</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6562,25 +6563,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>1110</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6593,10 +6594,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572347</v>
+        <v>572538</v>
       </c>
       <c r="R57" t="n">
-        <v>6462723</v>
+        <v>6462741</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,10 +6657,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123819022</v>
+        <v>123818763</v>
       </c>
       <c r="B58" t="n">
-        <v>91624</v>
+        <v>91010</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6668,25 +6669,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5454</v>
+        <v>1110</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6699,10 +6700,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572325</v>
+        <v>572392</v>
       </c>
       <c r="R58" t="n">
-        <v>6462706</v>
+        <v>6462722</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6762,10 +6763,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123819025</v>
+        <v>123818819</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>5479</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6778,27 +6779,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>101920</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6806,10 +6808,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572337</v>
+        <v>572399</v>
       </c>
       <c r="R59" t="n">
-        <v>6462716</v>
+        <v>6462693</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6869,10 +6871,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123818345</v>
+        <v>123818646</v>
       </c>
       <c r="B60" t="n">
-        <v>95705</v>
+        <v>79428</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6881,31 +6883,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6913,10 +6914,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572575</v>
+        <v>572466</v>
       </c>
       <c r="R60" t="n">
-        <v>6462706</v>
+        <v>6462822</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6976,10 +6977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819096</v>
+        <v>123819124</v>
       </c>
       <c r="B61" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6992,21 +6993,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7019,10 +7020,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572307</v>
+        <v>572362</v>
       </c>
       <c r="R61" t="n">
-        <v>6462856</v>
+        <v>6462874</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7082,10 +7083,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818843</v>
+        <v>123818916</v>
       </c>
       <c r="B62" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7098,21 +7099,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7125,10 +7126,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572420</v>
+        <v>572384</v>
       </c>
       <c r="R62" t="n">
-        <v>6462720</v>
+        <v>6462675</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7188,10 +7189,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123818837</v>
+        <v>123819084</v>
       </c>
       <c r="B63" t="n">
-        <v>91032</v>
+        <v>79428</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7204,21 +7205,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7231,10 +7232,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572414</v>
+        <v>572275</v>
       </c>
       <c r="R63" t="n">
-        <v>6462716</v>
+        <v>6462841</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,10 +7295,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123819032</v>
+        <v>123818843</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7310,21 +7311,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7337,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572284</v>
+        <v>572420</v>
       </c>
       <c r="R64" t="n">
-        <v>6462713</v>
+        <v>6462720</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7400,10 +7401,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123818454</v>
+        <v>123819179</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7412,31 +7413,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572542</v>
+        <v>572456</v>
       </c>
       <c r="R65" t="n">
-        <v>6462761</v>
+        <v>6462900</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818542</v>
+        <v>123818682</v>
       </c>
       <c r="B66" t="n">
         <v>57529</v>
@@ -7540,9 +7540,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7555,10 +7567,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572542</v>
+        <v>572441</v>
       </c>
       <c r="R66" t="n">
-        <v>6462761</v>
+        <v>6462802</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7591,6 +7603,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7617,7 +7634,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818682</v>
+        <v>123818542</v>
       </c>
       <c r="B67" t="n">
         <v>57529</v>
@@ -7650,21 +7667,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7677,10 +7682,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572441</v>
+        <v>572542</v>
       </c>
       <c r="R67" t="n">
-        <v>6462802</v>
+        <v>6462761</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7713,11 +7718,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7507,7 +7507,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818682</v>
+        <v>123818542</v>
       </c>
       <c r="B66" t="n">
         <v>57529</v>
@@ -7540,21 +7540,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7567,10 +7555,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572441</v>
+        <v>572542</v>
       </c>
       <c r="R66" t="n">
-        <v>6462802</v>
+        <v>6462761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7603,11 +7591,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7634,7 +7617,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818542</v>
+        <v>123818682</v>
       </c>
       <c r="B67" t="n">
         <v>57529</v>
@@ -7667,9 +7650,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -7682,10 +7677,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572542</v>
+        <v>572441</v>
       </c>
       <c r="R67" t="n">
-        <v>6462761</v>
+        <v>6462802</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7718,6 +7713,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7742,6 +7742,218 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129874725</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Jällsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>572342</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6462720</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>E-Åtv-0297</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129874728</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Jällsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>572538</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6462766</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>E-Åtv-0294</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7747,7 +7747,7 @@
         <v>129874725</v>
       </c>
       <c r="B68" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>129874728</v>
       </c>
       <c r="B69" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -7510,7 +7510,12 @@
         <v>123818542</v>
       </c>
       <c r="B66" t="n">
-        <v>57881</v>
+        <v>57529</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,7 +7620,12 @@
         <v>123818682</v>
       </c>
       <c r="B67" t="n">
-        <v>57881</v>
+        <v>57529</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123818757</v>
+        <v>123818639</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572407</v>
+        <v>572466</v>
       </c>
       <c r="R2" t="n">
-        <v>6462746</v>
+        <v>6462822</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123819022</v>
+        <v>123818753</v>
       </c>
       <c r="B3" t="n">
-        <v>91624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5454</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572325</v>
+        <v>572414</v>
       </c>
       <c r="R3" t="n">
-        <v>6462706</v>
+        <v>6462768</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123819025</v>
+        <v>123818843</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572337</v>
+        <v>572420</v>
       </c>
       <c r="R4" t="n">
-        <v>6462716</v>
+        <v>6462720</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123819173</v>
+        <v>123819073</v>
       </c>
       <c r="B5" t="n">
-        <v>92328</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572456</v>
+        <v>572257</v>
       </c>
       <c r="R5" t="n">
-        <v>6462900</v>
+        <v>6462806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123818852</v>
+        <v>123819077</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572410</v>
+        <v>572247</v>
       </c>
       <c r="R6" t="n">
-        <v>6462725</v>
+        <v>6462824</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,55 +1180,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123819121</v>
+        <v>123819082</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572362</v>
+        <v>572275</v>
       </c>
       <c r="R7" t="n">
-        <v>6462874</v>
+        <v>6462841</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,17 +1256,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spelplats?</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123819035</v>
+        <v>123819088</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572299</v>
+        <v>572276</v>
       </c>
       <c r="R8" t="n">
-        <v>6462763</v>
+        <v>6462860</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1435,43 +1382,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123818966</v>
+        <v>123819157</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1479,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572304</v>
+        <v>572446</v>
       </c>
       <c r="R9" t="n">
-        <v>6462690</v>
+        <v>6462925</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1542,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123819032</v>
+        <v>123819162</v>
       </c>
       <c r="B10" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572284</v>
+        <v>572447</v>
       </c>
       <c r="R10" t="n">
-        <v>6462713</v>
+        <v>6462925</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1648,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123819162</v>
+        <v>123819179</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572447</v>
+        <v>572456</v>
       </c>
       <c r="R11" t="n">
-        <v>6462925</v>
+        <v>6462900</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1754,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123818753</v>
+        <v>123818438</v>
       </c>
       <c r="B12" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1110</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572414</v>
+        <v>572538</v>
       </c>
       <c r="R12" t="n">
-        <v>6462768</v>
+        <v>6462741</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123819172</v>
+        <v>123818763</v>
       </c>
       <c r="B13" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572456</v>
+        <v>572392</v>
       </c>
       <c r="R13" t="n">
-        <v>6462900</v>
+        <v>6462722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1966,43 +1887,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123818415</v>
+        <v>123819172</v>
       </c>
       <c r="B14" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>1110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2010,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572570</v>
+        <v>572456</v>
       </c>
       <c r="R14" t="n">
-        <v>6462742</v>
+        <v>6462900</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,43 +1988,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123818936</v>
+        <v>123819035</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572347</v>
+        <v>572299</v>
       </c>
       <c r="R15" t="n">
-        <v>6462723</v>
+        <v>6462763</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2180,42 +2089,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123818360</v>
+        <v>123818345</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572567</v>
+        <v>572575</v>
       </c>
       <c r="R16" t="n">
-        <v>6462723</v>
+        <v>6462706</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2286,42 +2191,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123818590</v>
+        <v>123818415</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572563</v>
+        <v>572570</v>
       </c>
       <c r="R17" t="n">
-        <v>6462748</v>
+        <v>6462742</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2392,42 +2293,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123819072</v>
+        <v>123818629</v>
       </c>
       <c r="B18" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2435,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572298</v>
+        <v>572515</v>
       </c>
       <c r="R18" t="n">
-        <v>6462796</v>
+        <v>6462760</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2498,15 +2395,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123819088</v>
+        <v>123818426</v>
       </c>
       <c r="B19" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2406,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572276</v>
+        <v>572545</v>
       </c>
       <c r="R19" t="n">
-        <v>6462860</v>
+        <v>6462716</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2604,43 +2496,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123818742</v>
+        <v>123818873</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2648,10 +2534,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572433</v>
+        <v>572422</v>
       </c>
       <c r="R20" t="n">
-        <v>6462777</v>
+        <v>6462709</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2711,43 +2597,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123818629</v>
+        <v>123818381</v>
       </c>
       <c r="B21" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2755,10 +2635,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572515</v>
+        <v>572568</v>
       </c>
       <c r="R21" t="n">
-        <v>6462760</v>
+        <v>6462684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2818,37 +2698,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123818873</v>
+        <v>123818643</v>
       </c>
       <c r="B22" t="n">
-        <v>90996</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4660</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2861,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572422</v>
+        <v>572466</v>
       </c>
       <c r="R22" t="n">
-        <v>6462709</v>
+        <v>6462822</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,15 +2799,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819073</v>
+        <v>123818837</v>
       </c>
       <c r="B23" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2810,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572257</v>
+        <v>572414</v>
       </c>
       <c r="R23" t="n">
-        <v>6462806</v>
+        <v>6462716</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3030,15 +2900,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819157</v>
+        <v>123819096</v>
       </c>
       <c r="B24" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +2911,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +2938,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572446</v>
+        <v>572307</v>
       </c>
       <c r="R24" t="n">
-        <v>6462925</v>
+        <v>6462856</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3136,15 +3001,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819176</v>
+        <v>123819149</v>
       </c>
       <c r="B25" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,10 +3039,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572456</v>
+        <v>572405</v>
       </c>
       <c r="R25" t="n">
-        <v>6462900</v>
+        <v>6462934</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3242,15 +3102,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819077</v>
+        <v>123819167</v>
       </c>
       <c r="B26" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,21 +3113,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3285,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572247</v>
+        <v>572447</v>
       </c>
       <c r="R26" t="n">
-        <v>6462824</v>
+        <v>6462925</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3348,15 +3203,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123819082</v>
+        <v>123819176</v>
       </c>
       <c r="B27" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,21 +3214,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3391,10 +3241,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572275</v>
+        <v>572456</v>
       </c>
       <c r="R27" t="n">
-        <v>6462841</v>
+        <v>6462900</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3454,15 +3304,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123819167</v>
+        <v>123819022</v>
       </c>
       <c r="B28" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3470,21 +3315,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5454</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3342,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572447</v>
+        <v>572325</v>
       </c>
       <c r="R28" t="n">
-        <v>6462925</v>
+        <v>6462706</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3560,15 +3405,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123818837</v>
+        <v>123819173</v>
       </c>
       <c r="B29" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,21 +3416,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,10 +3443,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572414</v>
+        <v>572456</v>
       </c>
       <c r="R29" t="n">
-        <v>6462716</v>
+        <v>6462900</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3666,15 +3506,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123818960</v>
+        <v>123818938</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,35 +3517,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3718,10 +3544,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572326</v>
+        <v>572347</v>
       </c>
       <c r="R30" t="n">
-        <v>6462705</v>
+        <v>6462723</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,17 +3582,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta häckningsrevir</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3785,15 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123818388</v>
+        <v>123818331</v>
       </c>
       <c r="B31" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572560</v>
+        <v>572576</v>
       </c>
       <c r="R31" t="n">
-        <v>6462694</v>
+        <v>6462698</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3891,15 +3708,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123819089</v>
+        <v>123818360</v>
       </c>
       <c r="B32" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,10 +3746,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572276</v>
+        <v>572567</v>
       </c>
       <c r="R32" t="n">
-        <v>6462860</v>
+        <v>6462723</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3997,15 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123819036</v>
+        <v>123818371</v>
       </c>
       <c r="B33" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,10 +3847,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572299</v>
+        <v>572569</v>
       </c>
       <c r="R33" t="n">
-        <v>6462763</v>
+        <v>6462679</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4103,15 +3910,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123818331</v>
+        <v>123818388</v>
       </c>
       <c r="B34" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,10 +3948,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572576</v>
+        <v>572560</v>
       </c>
       <c r="R34" t="n">
-        <v>6462698</v>
+        <v>6462694</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4209,15 +4011,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123819169</v>
+        <v>123818590</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4252,10 +4049,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572447</v>
+        <v>572563</v>
       </c>
       <c r="R35" t="n">
-        <v>6462925</v>
+        <v>6462748</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4315,15 +4112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123819149</v>
+        <v>123818646</v>
       </c>
       <c r="B36" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4331,21 +4123,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4358,10 +4150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572405</v>
+        <v>572466</v>
       </c>
       <c r="R36" t="n">
-        <v>6462934</v>
+        <v>6462822</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4421,43 +4213,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123818446</v>
+        <v>123818757</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4465,10 +4251,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572535</v>
+        <v>572407</v>
       </c>
       <c r="R37" t="n">
-        <v>6462771</v>
+        <v>6462746</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4528,15 +4314,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123819158</v>
+        <v>123818826</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4571,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572446</v>
+        <v>572399</v>
       </c>
       <c r="R38" t="n">
-        <v>6462925</v>
+        <v>6462693</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4634,15 +4415,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123819034</v>
+        <v>123818852</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572277</v>
+        <v>572410</v>
       </c>
       <c r="R39" t="n">
-        <v>6462750</v>
+        <v>6462725</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4740,15 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123819074</v>
+        <v>123818916</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4783,10 +4554,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572257</v>
+        <v>572384</v>
       </c>
       <c r="R40" t="n">
-        <v>6462806</v>
+        <v>6462675</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4846,37 +4617,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123818938</v>
+        <v>123819032</v>
       </c>
       <c r="B41" t="n">
-        <v>74840</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4889,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572347</v>
+        <v>572284</v>
       </c>
       <c r="R41" t="n">
-        <v>6462723</v>
+        <v>6462713</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4952,43 +4718,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123818345</v>
+        <v>123819034</v>
       </c>
       <c r="B42" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4996,10 +4756,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572575</v>
+        <v>572277</v>
       </c>
       <c r="R42" t="n">
-        <v>6462706</v>
+        <v>6462750</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5059,43 +4819,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123818411</v>
+        <v>123819036</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5103,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572570</v>
+        <v>572299</v>
       </c>
       <c r="R43" t="n">
-        <v>6462742</v>
+        <v>6462763</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5166,15 +4920,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123819177</v>
+        <v>123819072</v>
       </c>
       <c r="B44" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5209,10 +4958,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572456</v>
+        <v>572298</v>
       </c>
       <c r="R44" t="n">
-        <v>6462900</v>
+        <v>6462796</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5272,15 +5021,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123818643</v>
+        <v>123819074</v>
       </c>
       <c r="B45" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5288,21 +5032,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5315,10 +5059,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572466</v>
+        <v>572257</v>
       </c>
       <c r="R45" t="n">
-        <v>6462822</v>
+        <v>6462806</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5378,15 +5122,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123819096</v>
+        <v>123819084</v>
       </c>
       <c r="B46" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5133,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5421,10 +5160,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572307</v>
+        <v>572275</v>
       </c>
       <c r="R46" t="n">
-        <v>6462856</v>
+        <v>6462841</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5484,15 +5223,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123818871</v>
+        <v>123819089</v>
       </c>
       <c r="B47" t="n">
-        <v>5492</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,28 +5234,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5529,10 +5261,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572422</v>
+        <v>572276</v>
       </c>
       <c r="R47" t="n">
-        <v>6462709</v>
+        <v>6462860</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5592,15 +5324,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123819031</v>
+        <v>123819098</v>
       </c>
       <c r="B48" t="n">
-        <v>5492</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,28 +5335,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5637,10 +5362,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572284</v>
+        <v>572307</v>
       </c>
       <c r="R48" t="n">
-        <v>6462713</v>
+        <v>6462856</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5700,15 +5425,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123819130</v>
+        <v>123819124</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572378</v>
+        <v>572362</v>
       </c>
       <c r="R49" t="n">
-        <v>6462897</v>
+        <v>6462874</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5806,15 +5526,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123818639</v>
+        <v>123819130</v>
       </c>
       <c r="B50" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5537,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5849,10 +5564,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572466</v>
+        <v>572378</v>
       </c>
       <c r="R50" t="n">
-        <v>6462822</v>
+        <v>6462897</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5912,15 +5627,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123818381</v>
+        <v>123819158</v>
       </c>
       <c r="B51" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5928,21 +5638,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5955,10 +5665,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572568</v>
+        <v>572446</v>
       </c>
       <c r="R51" t="n">
-        <v>6462684</v>
+        <v>6462925</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6018,15 +5728,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123819098</v>
+        <v>123819169</v>
       </c>
       <c r="B52" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572307</v>
+        <v>572447</v>
       </c>
       <c r="R52" t="n">
-        <v>6462856</v>
+        <v>6462925</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6124,43 +5829,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123818454</v>
+        <v>123819177</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6168,10 +5867,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572542</v>
+        <v>572456</v>
       </c>
       <c r="R53" t="n">
-        <v>6462761</v>
+        <v>6462900</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6231,15 +5930,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123818826</v>
+        <v>123819213</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6247,26 +5941,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100048</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6274,10 +5985,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572399</v>
+        <v>572473</v>
       </c>
       <c r="R54" t="n">
-        <v>6462693</v>
+        <v>6462886</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6318,7 +6029,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6337,15 +6047,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123818426</v>
+        <v>123818542</v>
       </c>
       <c r="B55" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6353,26 +6058,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6380,10 +6090,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572545</v>
+        <v>572542</v>
       </c>
       <c r="R55" t="n">
-        <v>6462716</v>
+        <v>6462761</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6424,7 +6134,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6443,44 +6152,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123819081</v>
+        <v>123818682</v>
       </c>
       <c r="B56" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6488,10 +6207,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572275</v>
+        <v>572441</v>
       </c>
       <c r="R56" t="n">
-        <v>6462841</v>
+        <v>6462802</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6526,13 +6245,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6551,42 +6274,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123818438</v>
+        <v>123819121</v>
       </c>
       <c r="B57" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1110</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6594,10 +6325,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572538</v>
+        <v>572362</v>
       </c>
       <c r="R57" t="n">
-        <v>6462741</v>
+        <v>6462874</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6632,13 +6363,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spelplats?</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6657,42 +6392,39 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123818763</v>
+        <v>123818871</v>
       </c>
       <c r="B58" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1110</v>
+        <v>101410</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6700,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572392</v>
+        <v>572422</v>
       </c>
       <c r="R58" t="n">
-        <v>6462722</v>
+        <v>6462709</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6763,37 +6495,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123818819</v>
+        <v>123819031</v>
       </c>
       <c r="B59" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>101920</v>
+        <v>101410</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6808,10 +6535,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572399</v>
+        <v>572284</v>
       </c>
       <c r="R59" t="n">
-        <v>6462693</v>
+        <v>6462713</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6871,42 +6598,39 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123818646</v>
+        <v>123818819</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6914,10 +6638,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572466</v>
+        <v>572399</v>
       </c>
       <c r="R60" t="n">
-        <v>6462822</v>
+        <v>6462693</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6977,42 +6701,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123819124</v>
+        <v>123819081</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>101920</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7020,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572362</v>
+        <v>572275</v>
       </c>
       <c r="R61" t="n">
-        <v>6462874</v>
+        <v>6462841</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7083,15 +6804,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123818916</v>
+        <v>123818960</v>
       </c>
       <c r="B62" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7099,26 +6815,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7126,10 +6851,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572384</v>
+        <v>572326</v>
       </c>
       <c r="R62" t="n">
-        <v>6462675</v>
+        <v>6462705</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7164,13 +6889,17 @@
           <t>2025-04-06</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta häckningsrevir</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7189,42 +6918,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123819084</v>
+        <v>123818411</v>
       </c>
       <c r="B63" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7232,10 +6957,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572275</v>
+        <v>572570</v>
       </c>
       <c r="R63" t="n">
-        <v>6462841</v>
+        <v>6462742</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7295,42 +7020,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123818843</v>
+        <v>123818446</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7338,10 +7059,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572420</v>
+        <v>572535</v>
       </c>
       <c r="R64" t="n">
-        <v>6462720</v>
+        <v>6462771</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,42 +7122,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123819179</v>
+        <v>123818454</v>
       </c>
       <c r="B65" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7444,10 +7161,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572456</v>
+        <v>572542</v>
       </c>
       <c r="R65" t="n">
-        <v>6462900</v>
+        <v>6462761</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7507,47 +7224,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123818542</v>
+        <v>123818742</v>
       </c>
       <c r="B66" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7555,10 +7263,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572542</v>
+        <v>572433</v>
       </c>
       <c r="R66" t="n">
-        <v>6462761</v>
+        <v>6462777</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7599,6 +7307,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7617,59 +7326,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123818682</v>
+        <v>123818936</v>
       </c>
       <c r="B67" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7677,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572441</v>
+        <v>572347</v>
       </c>
       <c r="R67" t="n">
-        <v>6462802</v>
+        <v>6462723</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7715,17 +7403,13 @@
           <t>2025-04-06</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>En hane I sitt permanenta revir, mycket hackspår annars i den 160 till 250 åriga naturskogen.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7744,10 +7428,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129874725</v>
+        <v>123818966</v>
       </c>
       <c r="B68" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7773,19 +7457,23 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jällsjön, Ög</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572342</v>
+        <v>572304</v>
       </c>
       <c r="R68" t="n">
-        <v>6462720</v>
+        <v>6462690</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7807,11 +7495,6 @@
           <t>Yxnerum</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>E-Åtv-0297</t>
-        </is>
-      </c>
       <c r="Y68" t="inlineStr">
         <is>
           <t>2025-04-06</t>
@@ -7828,13 +7511,14 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -7842,18 +7526,14 @@
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129874728</v>
+        <v>123819025</v>
       </c>
       <c r="B69" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7879,19 +7559,23 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jällsjön, Ög</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>572538</v>
+        <v>572337</v>
       </c>
       <c r="R69" t="n">
-        <v>6462766</v>
+        <v>6462716</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7913,11 +7597,6 @@
           <t>Yxnerum</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>E-Åtv-0294</t>
-        </is>
-      </c>
       <c r="Y69" t="inlineStr">
         <is>
           <t>2025-04-06</t>
@@ -7934,21 +7613,230 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129874725</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Jällsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>572342</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6462720</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>E-Åtv-0297</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
           <t>Karin Nyström</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129874728</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Jällsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>572538</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6462766</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>E-Åtv-0294</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 9114-2025 artfynd.xlsx
+++ b/artfynd/A 9114-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819077</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819082</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819088</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819157</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819162</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819179</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818438</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818763</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819035</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818345</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818415</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2392,6 +2477,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818629</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818426</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2594,6 +2689,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818381</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2796,6 +2901,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818643</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2897,6 +3007,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818837</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2998,6 +3113,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819096</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819149</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3200,6 +3325,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819167</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3301,6 +3431,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819176</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3503,6 +3643,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819173</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3604,6 +3749,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818938</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3705,6 +3855,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818331</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3806,6 +3961,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818360</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3907,6 +4067,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818371</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818388</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4109,6 +4279,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818590</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4210,6 +4385,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818646</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4311,6 +4491,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818757</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4412,6 +4597,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818826</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4513,6 +4703,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818852</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4614,6 +4809,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818916</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4715,6 +4915,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819032</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4816,6 +5021,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819034</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4917,6 +5127,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819036</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5018,6 +5233,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819072</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5119,6 +5339,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819074</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5220,6 +5445,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819084</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5321,6 +5551,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819089</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5422,6 +5657,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819098</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5523,6 +5763,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819124</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5624,6 +5869,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819130</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5725,6 +5975,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819158</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5826,6 +6081,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819169</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5927,6 +6187,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819177</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6044,6 +6309,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819213</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6149,6 +6419,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818542</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6271,6 +6546,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818682</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6389,6 +6669,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819121</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6492,6 +6777,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818871</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6595,6 +6885,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819031</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6698,6 +6993,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818819</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6801,6 +7101,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819081</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6915,6 +7220,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818960</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7017,6 +7327,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818411</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7119,6 +7434,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818446</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7221,6 +7541,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818454</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7323,6 +7648,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818742</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7425,6 +7755,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818936</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7527,6 +7862,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123818966</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7629,6 +7969,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7735,6 +8080,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874725</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7841,8 +8191,85 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129874728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>